--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D72EB97-B10C-44DD-B66F-BBA92B4B7B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86840465-08BB-4805-9E3B-67A25585C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,151 +817,175 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_004</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_015</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w210745193-220_HRV,e_w89817617-220_HRV,e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w170366194-220_HRV,e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV,e_w89819945-220_HRV,e_w89820062-400_HRV,e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV,e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV,e_w170366194-220_HRV,e_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w113757307-220_HRV,e_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV,e_w162022271-220_HRV,e_w43337263-400_HRV,e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV,e_w163860997-400_HRV,e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV,e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV,e_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w162022271-220_HRV,e_w43337263-220_HRV</t>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_003</t>
@@ -976,139 +1000,115 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_012</t>
   </si>
   <si>
     <t>elc_won_HRV_003</t>
   </si>
   <si>
-    <t>e_w210745193-220_HRV,e_w89817617-220_HRV</t>
+    <t>e_Pula_HRV,e_Viskovo_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_008</t>
   </si>
   <si>
-    <t>e_w113757307-220_HRV</t>
+    <t>e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_006</t>
   </si>
   <si>
-    <t>e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV,e_w273326173-220_HRV,e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>e_w89820062-400_HRV,e_w96704507-220_HRV</t>
+    <t>e_Ogulin_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_004</t>
   </si>
   <si>
-    <t>e_w210745193-220_HRV,e_w89817617-220_HRV,e_w89817617-400_HRV,e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_w89823918-400_HRV,e_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV,e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV,e_w89819945-220_HRV,e_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_012</t>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
     <t>e_won_HRV_001</t>
@@ -1291,7 +1291,7 @@
     <t>stepdown_w43337263_HRV_400to220</t>
   </si>
   <si>
-    <t>e_w43337263-400_HRV</t>
+    <t>e_KastelStari_HRV</t>
   </si>
   <si>
     <t>stepup_w43337263_HRV_220to400</t>
@@ -1300,10 +1300,10 @@
     <t>stepdown_w89817617_HRV_400to220</t>
   </si>
   <si>
-    <t>e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89817617-220_HRV</t>
+    <t>e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Viskovo_HRV</t>
   </si>
   <si>
     <t>stepup_w89817617_HRV_220to400</t>
@@ -1315,19 +1315,19 @@
     <t>capacityunit</t>
   </si>
   <si>
-    <t>Transformer: e_w43337263-400_HRV → e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>Transformer: e_w43337263-220_HRV → e_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>Transformer: e_w89817617-400_HRV → e_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>Transformer: e_w89817617-220_HRV → e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w113757307-220_HRV,e_w43337263-400_HRV,e_w89817617-400_HRV,e_w89818719-400_HRV,e_w89820062-220_HRV,e_w89820062-400_HRV,e_w89823918-400_HRV,e_w96704507-220_HRV,e_w96722667-220_HRV</t>
+    <t>Transformer: e_KastelStari_HRV → e_Split_HRV</t>
+  </si>
+  <si>
+    <t>Transformer: e_Split_HRV → e_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>Transformer: e_Rijeka_HRV → e_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>Transformer: e_Viskovo_HRV → e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_KastelStari_HRV,e_Kutina_HRV,e_Osijek_HRV,e_Rijeka_HRV,e_VelikaGorica_HRV,e_Vinkovci_HRV,e_Zagreb_HRV,e_w89820062-220_HRV,e_w96722667-220_HRV</t>
   </si>
 </sst>
 </file>
@@ -6100,7 +6100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C95047-7010-4CD2-AE73-2DF561740527}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0F380A-1E09-43C4-8276-DF683538BCAB}">
   <dimension ref="B9:AP25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6296,16 +6296,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99867337680137247</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB11">
-        <v>24.321425308170515</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6335,13 +6335,13 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="AO11">
-        <v>0.99790344697198585</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP11">
-        <v>38.436805513593036</v>
+        <v>26.570726762452622</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6406,16 +6406,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99878927154998876</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB12">
-        <v>22.196688250206851</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6442,16 +6442,16 @@
         <v>280</v>
       </c>
       <c r="AM12" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN12" t="s">
         <v>306</v>
       </c>
-      <c r="AN12" t="s">
-        <v>307</v>
-      </c>
       <c r="AO12">
-        <v>0.99831382084910869</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP12">
-        <v>30.913284433006623</v>
+        <v>62.127154430695668</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99790259024057815</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB13">
-        <v>38.452512256066314</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6552,16 +6552,16 @@
         <v>282</v>
       </c>
       <c r="AM13" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN13" t="s">
         <v>308</v>
       </c>
-      <c r="AN13" t="s">
-        <v>309</v>
-      </c>
       <c r="AO13">
-        <v>0.99696949512524791</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP13">
-        <v>55.559256037121919</v>
+        <v>24.097029967546128</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6626,16 +6626,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99744104449393167</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB14">
-        <v>46.914184277920093</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,16 +6662,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN14" t="s">
-        <v>311</v>
+        <v>273</v>
       </c>
       <c r="AO14">
-        <v>0.99831383758599213</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP14">
-        <v>30.912977590144003</v>
+        <v>73.382171124189711</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99817092025513499</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB15">
-        <v>33.533128655859528</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6772,16 +6772,16 @@
         <v>286</v>
       </c>
       <c r="AM15" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AN15" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="AO15">
-        <v>0.99916796132064933</v>
+        <v>0.99790344697198585</v>
       </c>
       <c r="AP15">
-        <v>15.254042454762756</v>
+        <v>38.436805513593036</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6846,16 +6846,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99608191256693812</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB16">
-        <v>71.831602939467288</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -6882,16 +6882,16 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
+        <v>312</v>
+      </c>
+      <c r="AN16" t="s">
         <v>313</v>
       </c>
-      <c r="AN16" t="s">
-        <v>264</v>
-      </c>
       <c r="AO16">
-        <v>0.99855068763113897</v>
+        <v>0.99831382084910869</v>
       </c>
       <c r="AP16">
-        <v>26.570726762452622</v>
+        <v>30.913284433006623</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6956,16 +6956,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99696148198205803</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB17">
-        <v>55.706163662270022</v>
+        <v>61.639327159526964</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -6998,10 +6998,10 @@
         <v>315</v>
       </c>
       <c r="AO17">
-        <v>0.99661124612196206</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP17">
-        <v>62.127154430695668</v>
+        <v>35.448029778312126</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7066,16 +7066,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99862410236781662</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB18">
-        <v>25.224789923361115</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7105,13 +7105,13 @@
         <v>316</v>
       </c>
       <c r="AN18" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="AO18">
-        <v>0.99842569630166256</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP18">
-        <v>28.86223446951988</v>
+        <v>15.254042454762756</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7176,16 +7176,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99833598914935617</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB19">
-        <v>30.506865595137178</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7212,16 +7212,16 @@
         <v>294</v>
       </c>
       <c r="AM19" t="s">
+        <v>317</v>
+      </c>
+      <c r="AN19" t="s">
         <v>318</v>
       </c>
-      <c r="AN19" t="s">
-        <v>319</v>
-      </c>
       <c r="AO19">
-        <v>0.99806647110300117</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP19">
-        <v>35.448029778312126</v>
+        <v>24.858866264948823</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7286,16 +7286,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99746297747029244</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB20">
-        <v>46.512079711305255</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7322,16 +7322,16 @@
         <v>296</v>
       </c>
       <c r="AM20" t="s">
+        <v>319</v>
+      </c>
+      <c r="AN20" t="s">
         <v>320</v>
       </c>
-      <c r="AN20" t="s">
-        <v>321</v>
-      </c>
       <c r="AO20">
-        <v>0.99864406184009369</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP20">
-        <v>24.858866264948823</v>
+        <v>30.912977590144003</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7396,16 +7396,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99841413454839123</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB21">
-        <v>29.074199946161183</v>
+        <v>71.831602939467288</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7432,10 +7432,10 @@
         <v>298</v>
       </c>
       <c r="AM21" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN21" t="s">
         <v>322</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>323</v>
       </c>
       <c r="AO21">
         <v>0.99309131353273861</v>
@@ -7506,16 +7506,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99606139674621874</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB22">
-        <v>72.207726319322958</v>
+        <v>55.706163662270022</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7542,16 +7542,16 @@
         <v>300</v>
       </c>
       <c r="AM22" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN22" t="s">
         <v>324</v>
       </c>
-      <c r="AN22" t="s">
-        <v>325</v>
-      </c>
       <c r="AO22">
-        <v>0.99868561654722476</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP22">
-        <v>24.097029967546128</v>
+        <v>55.559256037121919</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7616,16 +7616,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99752410262804614</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB23">
-        <v>45.391451819153936</v>
+        <v>46.512079711305255</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7652,16 +7652,16 @@
         <v>302</v>
       </c>
       <c r="AM23" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN23" t="s">
         <v>326</v>
       </c>
-      <c r="AN23" t="s">
-        <v>268</v>
-      </c>
       <c r="AO23">
-        <v>0.99599733612049879</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP23">
-        <v>73.382171124189711</v>
+        <v>28.86223446951988</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7726,16 +7726,16 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99663785488220757</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB24">
-        <v>61.639327159526964</v>
+        <v>24.321425308170515</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -7800,16 +7800,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99751404781443698</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB25">
-        <v>45.575790068655763</v>
+        <v>22.196688250206851</v>
       </c>
     </row>
   </sheetData>
@@ -7818,7 +7818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF55A7D-613C-400B-A909-426205908D10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B70F6FF-720E-4FA9-9D2B-4941136792FB}">
   <dimension ref="B9:M23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7891,7 +7891,7 @@
         <v>327</v>
       </c>
       <c r="K11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L11">
         <v>9.2886312097189838E-2</v>
@@ -7926,7 +7926,7 @@
         <v>329</v>
       </c>
       <c r="K12" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7961,7 +7961,7 @@
         <v>331</v>
       </c>
       <c r="K13" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L13">
         <v>0.2433090533988331</v>
@@ -7996,7 +7996,7 @@
         <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8031,7 +8031,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8066,7 +8066,7 @@
         <v>337</v>
       </c>
       <c r="K16" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8101,7 +8101,7 @@
         <v>339</v>
       </c>
       <c r="K17" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8136,7 +8136,7 @@
         <v>341</v>
       </c>
       <c r="K18" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="L18">
         <v>0.38607242074967713</v>
@@ -8171,7 +8171,7 @@
         <v>343</v>
       </c>
       <c r="K19" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8206,7 +8206,7 @@
         <v>345</v>
       </c>
       <c r="K20" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8241,7 +8241,7 @@
         <v>347</v>
       </c>
       <c r="K21" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8276,7 +8276,7 @@
         <v>349</v>
       </c>
       <c r="K22" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8311,7 +8311,7 @@
         <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,7 +8326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{764E689A-3DE8-4CEE-86C8-987FCA0B1713}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3CFD88-55F3-45E6-881A-6D8B11DC04C3}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11810,7 +11810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247526A5-F757-47C7-B2AD-09EDD524B279}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF34B5C7-0744-4966-B5AF-1CF810E14895}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11862,7 +11862,7 @@
         <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11891,7 +11891,7 @@
         <v>388</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D5" t="s">
         <v>387</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86840465-08BB-4805-9E3B-67A25585C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82AD3A7-671C-41E8-940D-69763BD4A880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,22 +817,76 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
+    <t>distr_solelc_spv_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_solelc_spv_HRV_005</t>
@@ -847,60 +901,6 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_004</t>
   </si>
   <si>
@@ -919,10 +919,37 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
     <t>e_Osijek_HRV</t>
   </si>
   <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
   </si>
   <si>
     <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
@@ -931,39 +958,36 @@
     <t>e_Kutina_HRV</t>
   </si>
   <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
     <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
   </si>
   <si>
     <t>e_Sisak_HRV,e_Kutina_HRV</t>
   </si>
   <si>
+    <t>distr_wonelc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_010</t>
   </si>
   <si>
@@ -976,16 +1000,28 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>distr_wonelc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_003</t>
@@ -1000,46 +1036,28 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
+    <t>elc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_010</t>
@@ -1051,13 +1069,28 @@
     <t>e_Zagreb_HRV,e_Kutina_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_012</t>
+    <t>elc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_003</t>
@@ -1072,43 +1105,10 @@
     <t>e_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
     <t>elc_won_HRV_006</t>
   </si>
   <si>
     <t>e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
     <t>e_won_HRV_001</t>
@@ -6100,7 +6100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A0F380A-1E09-43C4-8276-DF683538BCAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C43873-5749-4B1F-BF2F-BCA9451656BE}">
   <dimension ref="B9:AP25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6296,16 +6296,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99833598914935617</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB11">
-        <v>30.506865595137178</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6335,13 +6335,13 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AO11">
-        <v>0.99855068763113897</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP11">
-        <v>26.570726762452622</v>
+        <v>15.254042454762756</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6406,16 +6406,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99862410236781662</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB12">
-        <v>25.224789923361115</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6448,10 +6448,10 @@
         <v>306</v>
       </c>
       <c r="AO12">
-        <v>0.99661124612196206</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP12">
-        <v>62.127154430695668</v>
+        <v>24.097029967546128</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99841413454839123</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB13">
-        <v>29.074199946161183</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6555,13 +6555,13 @@
         <v>307</v>
       </c>
       <c r="AN13" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="AO13">
-        <v>0.99868561654722476</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP13">
-        <v>24.097029967546128</v>
+        <v>73.382171124189711</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6626,16 +6626,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99606139674621874</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB14">
-        <v>72.207726319322958</v>
+        <v>71.831602939467288</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,16 +6662,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
+        <v>308</v>
+      </c>
+      <c r="AN14" t="s">
         <v>309</v>
       </c>
-      <c r="AN14" t="s">
-        <v>273</v>
-      </c>
       <c r="AO14">
-        <v>0.99599733612049879</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP14">
-        <v>73.382171124189711</v>
+        <v>24.858866264948823</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99790259024057815</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB15">
-        <v>38.452512256066314</v>
+        <v>55.706163662270022</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6775,13 +6775,13 @@
         <v>310</v>
       </c>
       <c r="AN15" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="AO15">
-        <v>0.99790344697198585</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP15">
-        <v>38.436805513593036</v>
+        <v>26.570726762452622</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6846,16 +6846,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99752410262804614</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB16">
-        <v>45.391451819153936</v>
+        <v>46.512079711305255</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -6882,16 +6882,16 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
+        <v>311</v>
+      </c>
+      <c r="AN16" t="s">
         <v>312</v>
       </c>
-      <c r="AN16" t="s">
-        <v>313</v>
-      </c>
       <c r="AO16">
-        <v>0.99831382084910869</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP16">
-        <v>30.913284433006623</v>
+        <v>62.127154430695668</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6956,16 +6956,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99663785488220757</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB17">
-        <v>61.639327159526964</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -6992,16 +6992,16 @@
         <v>290</v>
       </c>
       <c r="AM17" t="s">
+        <v>313</v>
+      </c>
+      <c r="AN17" t="s">
         <v>314</v>
       </c>
-      <c r="AN17" t="s">
-        <v>315</v>
-      </c>
       <c r="AO17">
-        <v>0.99806647110300117</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP17">
-        <v>35.448029778312126</v>
+        <v>30.912977590144003</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7066,16 +7066,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99751404781443698</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB18">
-        <v>45.575790068655763</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7102,16 +7102,16 @@
         <v>292</v>
       </c>
       <c r="AM18" t="s">
+        <v>315</v>
+      </c>
+      <c r="AN18" t="s">
         <v>316</v>
       </c>
-      <c r="AN18" t="s">
-        <v>270</v>
-      </c>
       <c r="AO18">
-        <v>0.99916796132064933</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP18">
-        <v>15.254042454762756</v>
+        <v>35.448029778312126</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7176,16 +7176,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99744104449393167</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB19">
-        <v>46.914184277920093</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7218,10 +7218,10 @@
         <v>318</v>
       </c>
       <c r="AO19">
-        <v>0.99864406184009369</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP19">
-        <v>24.858866264948823</v>
+        <v>28.86223446951988</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7286,16 +7286,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99817092025513499</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB20">
-        <v>33.533128655859528</v>
+        <v>61.639327159526964</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7328,10 +7328,10 @@
         <v>320</v>
       </c>
       <c r="AO20">
-        <v>0.99831383758599213</v>
+        <v>0.99309131353273861</v>
       </c>
       <c r="AP20">
-        <v>30.912977590144003</v>
+        <v>126.6592518997923</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7396,16 +7396,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99608191256693812</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB21">
-        <v>71.831602939467288</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7438,10 +7438,10 @@
         <v>322</v>
       </c>
       <c r="AO21">
-        <v>0.99309131353273861</v>
+        <v>0.99790344697198585</v>
       </c>
       <c r="AP21">
-        <v>126.6592518997923</v>
+        <v>38.436805513593036</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -7506,16 +7506,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99696148198205803</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB22">
-        <v>55.706163662270022</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7548,10 +7548,10 @@
         <v>324</v>
       </c>
       <c r="AO22">
-        <v>0.99696949512524791</v>
+        <v>0.99831382084910869</v>
       </c>
       <c r="AP22">
-        <v>55.559256037121919</v>
+        <v>30.913284433006623</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7616,16 +7616,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99746297747029244</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB23">
-        <v>46.512079711305255</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7658,10 +7658,10 @@
         <v>326</v>
       </c>
       <c r="AO23">
-        <v>0.99842569630166256</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP23">
-        <v>28.86223446951988</v>
+        <v>55.559256037121919</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7818,7 +7818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B70F6FF-720E-4FA9-9D2B-4941136792FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352F58D2-8B6D-49E4-86C0-9FB972C9F872}">
   <dimension ref="B9:M23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7891,7 +7891,7 @@
         <v>327</v>
       </c>
       <c r="K11" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L11">
         <v>9.2886312097189838E-2</v>
@@ -7926,7 +7926,7 @@
         <v>329</v>
       </c>
       <c r="K12" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7961,7 +7961,7 @@
         <v>331</v>
       </c>
       <c r="K13" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L13">
         <v>0.2433090533988331</v>
@@ -7996,7 +7996,7 @@
         <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8031,7 +8031,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8066,7 +8066,7 @@
         <v>337</v>
       </c>
       <c r="K16" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8101,7 +8101,7 @@
         <v>339</v>
       </c>
       <c r="K17" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8136,7 +8136,7 @@
         <v>341</v>
       </c>
       <c r="K18" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="L18">
         <v>0.38607242074967713</v>
@@ -8171,7 +8171,7 @@
         <v>343</v>
       </c>
       <c r="K19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8206,7 +8206,7 @@
         <v>345</v>
       </c>
       <c r="K20" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8241,7 +8241,7 @@
         <v>347</v>
       </c>
       <c r="K21" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8276,7 +8276,7 @@
         <v>349</v>
       </c>
       <c r="K22" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8311,7 +8311,7 @@
         <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,7 +8326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3CFD88-55F3-45E6-881A-6D8B11DC04C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A4848B-7C9B-46AE-B49B-FD241E6EAD1E}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11810,7 +11810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF34B5C7-0744-4966-B5AF-1CF810E14895}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EC66E0-6805-4132-9362-38AE65C5838F}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11862,7 +11862,7 @@
         <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11891,7 +11891,7 @@
         <v>388</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
         <v>387</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D82AD3A7-671C-41E8-940D-69763BD4A880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73790DB0-E6D2-45C9-B7AD-15184986F5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,60 +817,90 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_003</t>
   </si>
   <si>
@@ -883,85 +913,73 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
     <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
   </si>
   <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV</t>
-  </si>
-  <si>
     <t>e_Pula_HRV</t>
   </si>
   <si>
     <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+    <t>distr_wonelc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_002</t>
@@ -970,6 +988,48 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_011</t>
   </si>
   <si>
@@ -982,69 +1042,66 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
+    <t>elc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_002</t>
   </si>
   <si>
+    <t>elc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_003</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_008</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
     <t>elc_won_HRV_011</t>
   </si>
   <si>
@@ -1052,63 +1109,6 @@
   </si>
   <si>
     <t>elc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_003</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_008</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV</t>
   </si>
   <si>
     <t>e_won_HRV_001</t>
@@ -6100,7 +6100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C43873-5749-4B1F-BF2F-BCA9451656BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B7DE5F-4C5A-4C30-907F-0A9364BD24B9}">
   <dimension ref="B9:AP25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6296,16 +6296,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99862410236781662</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB11">
-        <v>25.224789923361115</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6338,10 +6338,10 @@
         <v>273</v>
       </c>
       <c r="AO11">
-        <v>0.99916796132064933</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP11">
-        <v>15.254042454762756</v>
+        <v>26.570726762452622</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6406,16 +6406,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99744104449393167</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB12">
-        <v>46.914184277920093</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6448,10 +6448,10 @@
         <v>306</v>
       </c>
       <c r="AO12">
-        <v>0.99868561654722476</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP12">
-        <v>24.097029967546128</v>
+        <v>62.127154430695668</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99817092025513499</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB13">
-        <v>33.533128655859528</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6555,13 +6555,13 @@
         <v>307</v>
       </c>
       <c r="AN13" t="s">
-        <v>266</v>
+        <v>308</v>
       </c>
       <c r="AO13">
-        <v>0.99599733612049879</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP13">
-        <v>73.382171124189711</v>
+        <v>30.912977590144003</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6626,16 +6626,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99608191256693812</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB14">
-        <v>71.831602939467288</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,16 +6662,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AN14" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="AO14">
-        <v>0.99864406184009369</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP14">
-        <v>24.858866264948823</v>
+        <v>15.254042454762756</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99696148198205803</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB15">
-        <v>55.706163662270022</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6775,13 +6775,13 @@
         <v>310</v>
       </c>
       <c r="AN15" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="AO15">
-        <v>0.99855068763113897</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP15">
-        <v>26.570726762452622</v>
+        <v>28.86223446951988</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6846,16 +6846,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99746297747029244</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB16">
-        <v>46.512079711305255</v>
+        <v>71.831602939467288</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -6882,16 +6882,16 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO16">
-        <v>0.99661124612196206</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP16">
-        <v>62.127154430695668</v>
+        <v>55.559256037121919</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6956,16 +6956,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99790259024057815</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB17">
-        <v>38.452512256066314</v>
+        <v>55.706163662270022</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -6992,16 +6992,16 @@
         <v>290</v>
       </c>
       <c r="AM17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AN17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO17">
-        <v>0.99831383758599213</v>
+        <v>0.99790344697198585</v>
       </c>
       <c r="AP17">
-        <v>30.912977590144003</v>
+        <v>38.436805513593036</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7066,16 +7066,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99833598914935617</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB18">
-        <v>30.506865595137178</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7102,16 +7102,16 @@
         <v>292</v>
       </c>
       <c r="AM18" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO18">
-        <v>0.99806647110300117</v>
+        <v>0.99831382084910869</v>
       </c>
       <c r="AP18">
-        <v>35.448029778312126</v>
+        <v>30.913284433006623</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7176,16 +7176,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99752410262804614</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB19">
-        <v>45.391451819153936</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7212,16 +7212,16 @@
         <v>294</v>
       </c>
       <c r="AM19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO19">
-        <v>0.99842569630166256</v>
+        <v>0.99309131353273861</v>
       </c>
       <c r="AP19">
-        <v>28.86223446951988</v>
+        <v>126.6592518997923</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7286,16 +7286,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99663785488220757</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB20">
-        <v>61.639327159526964</v>
+        <v>24.321425308170515</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7322,16 +7322,16 @@
         <v>296</v>
       </c>
       <c r="AM20" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO20">
-        <v>0.99309131353273861</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP20">
-        <v>126.6592518997923</v>
+        <v>24.858866264948823</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7396,16 +7396,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99751404781443698</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB21">
-        <v>45.575790068655763</v>
+        <v>22.196688250206851</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7432,16 +7432,16 @@
         <v>298</v>
       </c>
       <c r="AM21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AN21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AO21">
-        <v>0.99790344697198585</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP21">
-        <v>38.436805513593036</v>
+        <v>35.448029778312126</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -7506,16 +7506,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99841413454839123</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB22">
-        <v>29.074199946161183</v>
+        <v>46.512079711305255</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7542,16 +7542,16 @@
         <v>300</v>
       </c>
       <c r="AM22" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO22">
-        <v>0.99831382084910869</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP22">
-        <v>30.913284433006623</v>
+        <v>24.097029967546128</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7616,16 +7616,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99606139674621874</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB23">
-        <v>72.207726319322958</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7652,16 +7652,16 @@
         <v>302</v>
       </c>
       <c r="AM23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN23" t="s">
-        <v>326</v>
+        <v>268</v>
       </c>
       <c r="AO23">
-        <v>0.99696949512524791</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP23">
-        <v>55.559256037121919</v>
+        <v>73.382171124189711</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7726,16 +7726,16 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99867337680137247</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB24">
-        <v>24.321425308170515</v>
+        <v>45.391451819153936</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -7800,16 +7800,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99878927154998876</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB25">
-        <v>22.196688250206851</v>
+        <v>61.639327159526964</v>
       </c>
     </row>
   </sheetData>
@@ -7818,7 +7818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352F58D2-8B6D-49E4-86C0-9FB972C9F872}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73270DCC-10CC-40AB-B25A-38BF67A76C45}">
   <dimension ref="B9:M23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7891,7 +7891,7 @@
         <v>327</v>
       </c>
       <c r="K11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L11">
         <v>9.2886312097189838E-2</v>
@@ -7926,7 +7926,7 @@
         <v>329</v>
       </c>
       <c r="K12" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7961,7 +7961,7 @@
         <v>331</v>
       </c>
       <c r="K13" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L13">
         <v>0.2433090533988331</v>
@@ -7996,7 +7996,7 @@
         <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8031,7 +8031,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8066,7 +8066,7 @@
         <v>337</v>
       </c>
       <c r="K16" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8101,7 +8101,7 @@
         <v>339</v>
       </c>
       <c r="K17" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8136,7 +8136,7 @@
         <v>341</v>
       </c>
       <c r="K18" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="L18">
         <v>0.38607242074967713</v>
@@ -8171,7 +8171,7 @@
         <v>343</v>
       </c>
       <c r="K19" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8206,7 +8206,7 @@
         <v>345</v>
       </c>
       <c r="K20" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8241,7 +8241,7 @@
         <v>347</v>
       </c>
       <c r="K21" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8276,7 +8276,7 @@
         <v>349</v>
       </c>
       <c r="K22" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8311,7 +8311,7 @@
         <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,7 +8326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5A4848B-7C9B-46AE-B49B-FD241E6EAD1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CD9061-511D-4949-83F2-86521EBE5748}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11810,7 +11810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96EC66E0-6805-4132-9362-38AE65C5838F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00892CA-218D-4E9A-9CAD-827320E36C8A}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11862,7 +11862,7 @@
         <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11891,7 +11891,7 @@
         <v>388</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D5" t="s">
         <v>387</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73790DB0-E6D2-45C9-B7AD-15184986F5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8510709B-D846-4C1B-B155-71D9C8DC9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -835,12 +835,60 @@
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_006</t>
   </si>
   <si>
@@ -865,54 +913,6 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -925,9 +925,33 @@
     <t>e_Kutina_HRV</t>
   </si>
   <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
     <t>e_Osijek_HRV</t>
   </si>
   <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
     <t>e_Knin_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
@@ -940,28 +964,64 @@
     <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
   </si>
   <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Sisak_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+    <t>distr_wonelc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_010</t>
@@ -976,70 +1036,67 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
+    <t>elc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_003</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_008</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_010</t>
@@ -1051,64 +1108,7 @@
     <t>e_Zagreb_HRV,e_Kutina_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
     <t>elc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_003</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_008</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_012</t>
   </si>
   <si>
     <t>e_won_HRV_001</t>
@@ -6100,7 +6100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B7DE5F-4C5A-4C30-907F-0A9364BD24B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA78E780-4788-44FD-A757-7053946BB2B9}">
   <dimension ref="B9:AP25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6335,13 +6335,13 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="AO11">
-        <v>0.99855068763113897</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP11">
-        <v>26.570726762452622</v>
+        <v>30.912977590144003</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6442,16 +6442,16 @@
         <v>280</v>
       </c>
       <c r="AM12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO12">
-        <v>0.99661124612196206</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP12">
-        <v>62.127154430695668</v>
+        <v>28.86223446951988</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99833598914935617</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB13">
-        <v>30.506865595137178</v>
+        <v>24.321425308170515</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6552,16 +6552,16 @@
         <v>282</v>
       </c>
       <c r="AM13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO13">
-        <v>0.99831383758599213</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP13">
-        <v>30.912977590144003</v>
+        <v>24.858866264948823</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6626,16 +6626,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99744104449393167</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB14">
-        <v>46.914184277920093</v>
+        <v>22.196688250206851</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,16 +6662,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN14" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="AO14">
-        <v>0.99916796132064933</v>
+        <v>0.99790344697198585</v>
       </c>
       <c r="AP14">
-        <v>15.254042454762756</v>
+        <v>38.436805513593036</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99817092025513499</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB15">
-        <v>33.533128655859528</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6772,16 +6772,16 @@
         <v>286</v>
       </c>
       <c r="AM15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO15">
-        <v>0.99842569630166256</v>
+        <v>0.99831382084910869</v>
       </c>
       <c r="AP15">
-        <v>28.86223446951988</v>
+        <v>30.913284433006623</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6846,16 +6846,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99608191256693812</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB16">
-        <v>71.831602939467288</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -6882,10 +6882,10 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AN16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AO16">
         <v>0.99696949512524791</v>
@@ -6956,16 +6956,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99696148198205803</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB17">
-        <v>55.706163662270022</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -6992,16 +6992,16 @@
         <v>290</v>
       </c>
       <c r="AM17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO17">
-        <v>0.99790344697198585</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP17">
-        <v>38.436805513593036</v>
+        <v>24.097029967546128</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7066,16 +7066,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99751404781443698</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB18">
-        <v>45.575790068655763</v>
+        <v>46.512079711305255</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7102,16 +7102,16 @@
         <v>292</v>
       </c>
       <c r="AM18" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN18" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="AO18">
-        <v>0.99831382084910869</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP18">
-        <v>30.913284433006623</v>
+        <v>73.382171124189711</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7176,16 +7176,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99790259024057815</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB19">
-        <v>38.452512256066314</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7212,10 +7212,10 @@
         <v>294</v>
       </c>
       <c r="AM19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO19">
         <v>0.99309131353273861</v>
@@ -7286,16 +7286,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99867337680137247</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB20">
-        <v>24.321425308170515</v>
+        <v>61.639327159526964</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7322,16 +7322,16 @@
         <v>296</v>
       </c>
       <c r="AM20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN20" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO20">
-        <v>0.99864406184009369</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP20">
-        <v>24.858866264948823</v>
+        <v>35.448029778312126</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7396,16 +7396,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99878927154998876</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB21">
-        <v>22.196688250206851</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7432,16 +7432,16 @@
         <v>298</v>
       </c>
       <c r="AM21" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN21" t="s">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="AO21">
-        <v>0.99806647110300117</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP21">
-        <v>35.448029778312126</v>
+        <v>26.570726762452622</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -7506,16 +7506,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99746297747029244</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB22">
-        <v>46.512079711305255</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7548,10 +7548,10 @@
         <v>325</v>
       </c>
       <c r="AO22">
-        <v>0.99868561654722476</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP22">
-        <v>24.097029967546128</v>
+        <v>62.127154430695668</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7616,16 +7616,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99862410236781662</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB23">
-        <v>25.224789923361115</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7655,13 +7655,13 @@
         <v>326</v>
       </c>
       <c r="AN23" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AO23">
-        <v>0.99599733612049879</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP23">
-        <v>73.382171124189711</v>
+        <v>15.254042454762756</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7726,16 +7726,16 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99752410262804614</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB24">
-        <v>45.391451819153936</v>
+        <v>71.831602939467288</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -7800,16 +7800,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99663785488220757</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB25">
-        <v>61.639327159526964</v>
+        <v>55.706163662270022</v>
       </c>
     </row>
   </sheetData>
@@ -7818,7 +7818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73270DCC-10CC-40AB-B25A-38BF67A76C45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABAE68F-F15C-4698-AF7A-666A8D6D50FF}">
   <dimension ref="B9:M23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7891,7 +7891,7 @@
         <v>327</v>
       </c>
       <c r="K11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L11">
         <v>9.2886312097189838E-2</v>
@@ -7926,7 +7926,7 @@
         <v>329</v>
       </c>
       <c r="K12" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7961,7 +7961,7 @@
         <v>331</v>
       </c>
       <c r="K13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L13">
         <v>0.2433090533988331</v>
@@ -7996,7 +7996,7 @@
         <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8031,7 +8031,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8066,7 +8066,7 @@
         <v>337</v>
       </c>
       <c r="K16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8101,7 +8101,7 @@
         <v>339</v>
       </c>
       <c r="K17" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8136,7 +8136,7 @@
         <v>341</v>
       </c>
       <c r="K18" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="L18">
         <v>0.38607242074967713</v>
@@ -8171,7 +8171,7 @@
         <v>343</v>
       </c>
       <c r="K19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8206,7 +8206,7 @@
         <v>345</v>
       </c>
       <c r="K20" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8241,7 +8241,7 @@
         <v>347</v>
       </c>
       <c r="K21" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8276,7 +8276,7 @@
         <v>349</v>
       </c>
       <c r="K22" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8311,7 +8311,7 @@
         <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,7 +8326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CD9061-511D-4949-83F2-86521EBE5748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FBEE73-BFEC-4F5C-BF1F-26E7981B5065}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11810,7 +11810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00892CA-218D-4E9A-9CAD-827320E36C8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB2B51C-8CE0-43A9-B057-E81F4296FB93}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11862,7 +11862,7 @@
         <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -11891,7 +11891,7 @@
         <v>388</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
         <v>387</v>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8510709B-D846-4C1B-B155-71D9C8DC9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05B4F40E-F93D-45E7-926D-1E324B568745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,18 +817,72 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_005</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 5</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_014</t>
   </si>
   <si>
@@ -847,78 +901,51 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
     <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
   </si>
   <si>
@@ -931,37 +958,28 @@
     <t>e_Sisak_HRV,e_Kutina_HRV</t>
   </si>
   <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
-  </si>
-  <si>
     <t>e_Osijek_HRV</t>
   </si>
   <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
     <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
-    <t>e_Pula_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+    <t>distr_wonelc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_007</t>
@@ -970,16 +988,46 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_003</t>
@@ -994,52 +1042,19 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>elc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_007</t>
@@ -1048,16 +1063,40 @@
     <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
+    <t>elc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_002</t>
+  </si>
+  <si>
     <t>elc_won_HRV_004</t>
   </si>
   <si>
     <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_003</t>
@@ -1070,45 +1109,6 @@
   </si>
   <si>
     <t>e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_002</t>
   </si>
   <si>
     <t>e_won_HRV_001</t>
@@ -6100,7 +6100,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA78E780-4788-44FD-A757-7053946BB2B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E304EB98-523F-4B42-9932-94344BF13789}">
   <dimension ref="B9:AP25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6296,16 +6296,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99841413454839123</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB11">
-        <v>29.074199946161183</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6335,13 +6335,13 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="AO11">
-        <v>0.99831383758599213</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP11">
-        <v>30.912977590144003</v>
+        <v>26.570726762452622</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6406,16 +6406,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99606139674621874</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB12">
-        <v>72.207726319322958</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6442,16 +6442,16 @@
         <v>280</v>
       </c>
       <c r="AM12" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN12" t="s">
         <v>306</v>
       </c>
-      <c r="AN12" t="s">
-        <v>307</v>
-      </c>
       <c r="AO12">
-        <v>0.99842569630166256</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP12">
-        <v>28.86223446951988</v>
+        <v>62.127154430695668</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99867337680137247</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB13">
-        <v>24.321425308170515</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6552,16 +6552,16 @@
         <v>282</v>
       </c>
       <c r="AM13" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN13" t="s">
         <v>308</v>
       </c>
-      <c r="AN13" t="s">
-        <v>309</v>
-      </c>
       <c r="AO13">
-        <v>0.99864406184009369</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP13">
-        <v>24.858866264948823</v>
+        <v>35.448029778312126</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6626,16 +6626,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99878927154998876</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB14">
-        <v>22.196688250206851</v>
+        <v>71.831602939467288</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,16 +6662,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
+        <v>309</v>
+      </c>
+      <c r="AN14" t="s">
         <v>310</v>
       </c>
-      <c r="AN14" t="s">
-        <v>311</v>
-      </c>
       <c r="AO14">
-        <v>0.99790344697198585</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP14">
-        <v>38.436805513593036</v>
+        <v>30.912977590144003</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99862410236781662</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB15">
-        <v>25.224789923361115</v>
+        <v>55.706163662270022</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6772,16 +6772,16 @@
         <v>286</v>
       </c>
       <c r="AM15" t="s">
+        <v>311</v>
+      </c>
+      <c r="AN15" t="s">
         <v>312</v>
       </c>
-      <c r="AN15" t="s">
-        <v>313</v>
-      </c>
       <c r="AO15">
-        <v>0.99831382084910869</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP15">
-        <v>30.913284433006623</v>
+        <v>24.097029967546128</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6846,16 +6846,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99833598914935617</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB16">
-        <v>30.506865595137178</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -6882,16 +6882,16 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AN16" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="AO16">
-        <v>0.99696949512524791</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP16">
-        <v>55.559256037121919</v>
+        <v>73.382171124189711</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6956,16 +6956,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99790259024057815</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB17">
-        <v>38.452512256066314</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -6992,16 +6992,16 @@
         <v>290</v>
       </c>
       <c r="AM17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AN17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AO17">
-        <v>0.99868561654722476</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP17">
-        <v>24.097029967546128</v>
+        <v>24.858866264948823</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7066,16 +7066,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99746297747029244</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB18">
-        <v>46.512079711305255</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7102,16 +7102,16 @@
         <v>292</v>
       </c>
       <c r="AM18" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AN18" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AO18">
-        <v>0.99599733612049879</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP18">
-        <v>73.382171124189711</v>
+        <v>15.254042454762756</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7176,16 +7176,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99752410262804614</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB19">
-        <v>45.391451819153936</v>
+        <v>61.639327159526964</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7212,16 +7212,16 @@
         <v>294</v>
       </c>
       <c r="AM19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AN19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AO19">
-        <v>0.99309131353273861</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP19">
-        <v>126.6592518997923</v>
+        <v>28.86223446951988</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7286,16 +7286,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99663785488220757</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB20">
-        <v>61.639327159526964</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7322,16 +7322,16 @@
         <v>296</v>
       </c>
       <c r="AM20" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AN20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AO20">
-        <v>0.99806647110300117</v>
+        <v>0.99309131353273861</v>
       </c>
       <c r="AP20">
-        <v>35.448029778312126</v>
+        <v>126.6592518997923</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7396,16 +7396,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99751404781443698</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB21">
-        <v>45.575790068655763</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7432,16 +7432,16 @@
         <v>298</v>
       </c>
       <c r="AM21" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AN21" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="AO21">
-        <v>0.99855068763113897</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP21">
-        <v>26.570726762452622</v>
+        <v>55.559256037121919</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -7506,16 +7506,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99744104449393167</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB22">
-        <v>46.914184277920093</v>
+        <v>24.321425308170515</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7542,16 +7542,16 @@
         <v>300</v>
       </c>
       <c r="AM22" t="s">
+        <v>323</v>
+      </c>
+      <c r="AN22" t="s">
         <v>324</v>
       </c>
-      <c r="AN22" t="s">
-        <v>325</v>
-      </c>
       <c r="AO22">
-        <v>0.99661124612196206</v>
+        <v>0.99790344697198585</v>
       </c>
       <c r="AP22">
-        <v>62.127154430695668</v>
+        <v>38.436805513593036</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7616,16 +7616,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99817092025513499</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB23">
-        <v>33.533128655859528</v>
+        <v>22.196688250206851</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7652,16 +7652,16 @@
         <v>302</v>
       </c>
       <c r="AM23" t="s">
+        <v>325</v>
+      </c>
+      <c r="AN23" t="s">
         <v>326</v>
       </c>
-      <c r="AN23" t="s">
-        <v>273</v>
-      </c>
       <c r="AO23">
-        <v>0.99916796132064933</v>
+        <v>0.99831382084910869</v>
       </c>
       <c r="AP23">
-        <v>15.254042454762756</v>
+        <v>30.913284433006623</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7726,16 +7726,16 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99608191256693812</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB24">
-        <v>71.831602939467288</v>
+        <v>30.506865595137178</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -7800,16 +7800,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99696148198205803</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB25">
-        <v>55.706163662270022</v>
+        <v>46.512079711305255</v>
       </c>
     </row>
   </sheetData>
@@ -7818,7 +7818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ABAE68F-F15C-4698-AF7A-666A8D6D50FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E4E7B2-2305-4E3D-A8E9-9AC35F65F775}">
   <dimension ref="B9:M23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7926,7 +7926,7 @@
         <v>329</v>
       </c>
       <c r="K12" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7961,7 +7961,7 @@
         <v>331</v>
       </c>
       <c r="K13" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="L13">
         <v>0.2433090533988331</v>
@@ -7996,7 +7996,7 @@
         <v>333</v>
       </c>
       <c r="K14" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8031,7 +8031,7 @@
         <v>335</v>
       </c>
       <c r="K15" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8066,7 +8066,7 @@
         <v>337</v>
       </c>
       <c r="K16" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8101,7 +8101,7 @@
         <v>339</v>
       </c>
       <c r="K17" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8136,7 +8136,7 @@
         <v>341</v>
       </c>
       <c r="K18" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="L18">
         <v>0.38607242074967713</v>
@@ -8171,7 +8171,7 @@
         <v>343</v>
       </c>
       <c r="K19" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8206,7 +8206,7 @@
         <v>345</v>
       </c>
       <c r="K20" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8241,7 +8241,7 @@
         <v>347</v>
       </c>
       <c r="K21" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8276,7 +8276,7 @@
         <v>349</v>
       </c>
       <c r="K22" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8311,7 +8311,7 @@
         <v>351</v>
       </c>
       <c r="K23" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,7 +8326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FBEE73-BFEC-4F5C-BF1F-26E7981B5065}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0F46F0-1E13-478C-AF55-7CA9C08BED4B}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11810,7 +11810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB2B51C-8CE0-43A9-B057-E81F4296FB93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780EB405-1306-498B-8ECF-F0CAF0815027}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05B4F40E-F93D-45E7-926D-1E324B568745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C86AF1F9-7875-471F-980E-22BF138F4F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -21,9 +21,10 @@
     <sheet name="wind" sheetId="13" r:id="rId6"/>
     <sheet name="conventional" sheetId="14" r:id="rId7"/>
     <sheet name="grid_transformers" sheetId="15" r:id="rId8"/>
+    <sheet name="co2_network" sheetId="16" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
     <definedName name="FuelList">[1]ELC_Lists!$K$4:$K$113</definedName>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1983" uniqueCount="522">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -817,16 +818,76 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_solelc_spv_HRV_006</t>
@@ -853,75 +914,45 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
     <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
   </si>
   <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
     <t>e_Knin_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
@@ -934,34 +965,28 @@
     <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
   </si>
   <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Sisak_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
+    <t>distr_wonelc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_010</t>
@@ -976,18 +1001,6 @@
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_011</t>
   </si>
   <si>
@@ -1000,16 +1013,16 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>distr_wonelc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_004</t>
@@ -1018,18 +1031,6 @@
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_003</t>
   </si>
   <si>
@@ -1042,6 +1043,27 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_won_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_007</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_009</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_002</t>
+  </si>
+  <si>
     <t>elc_won_HRV_010</t>
   </si>
   <si>
@@ -1051,18 +1073,6 @@
     <t>e_Zagreb_HRV,e_Kutina_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_009</t>
-  </si>
-  <si>
-    <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_007</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
     <t>elc_won_HRV_011</t>
   </si>
   <si>
@@ -1072,13 +1082,16 @@
     <t>elc_won_HRV_012</t>
   </si>
   <si>
-    <t>elc_won_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_002</t>
+    <t>elc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
   </si>
   <si>
     <t>elc_won_HRV_004</t>
@@ -1087,18 +1100,6 @@
     <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV</t>
-  </si>
-  <si>
     <t>elc_won_HRV_003</t>
   </si>
   <si>
@@ -1111,6 +1112,111 @@
     <t>e_Vinkovci_HRV</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
     <t>e_won_HRV_001</t>
   </si>
   <si>
@@ -1189,6 +1295,72 @@
     <t>wind resource in cluster 13</t>
   </si>
   <si>
+    <t>e_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 1</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 2</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 3</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 4</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 5</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 6</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 7</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 8</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 9</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 10</t>
+  </si>
+  <si>
+    <t>e_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>wind offshore resource in cluster 11</t>
+  </si>
+  <si>
     <t>~fi_t: UP</t>
   </si>
   <si>
@@ -1328,6 +1500,201 @@
   </si>
   <si>
     <t>e_KastelStari_HRV,e_Kutina_HRV,e_Osijek_HRV,e_Rijeka_HRV,e_VelikaGorica_HRV,e_Vinkovci_HRV,e_Zagreb_HRV,e_w89820062-220_HRV,e_w96722667-220_HRV</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>cement_Pula_HRV</t>
+  </si>
+  <si>
+    <t>HRV</t>
+  </si>
+  <si>
+    <t>capturable co2: cement (1 sites, 595 kt/yr)</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>cement_Split_HRV</t>
+  </si>
+  <si>
+    <t>capturable co2: cement (2 sites, 1427 kt/yr)</t>
+  </si>
+  <si>
+    <t>cement_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>capturable co2: cement (1 sites, 65 kt/yr)</t>
+  </si>
+  <si>
+    <t>sto_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10893.0 (OGCI/catalogue, 310 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10894.0 (OGCI/catalogue, 270 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10895.0 (OGCI/catalogue, 282 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10896.0 (OGCI/catalogue, 3361 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10897.0 (OGCI/catalogue, 143 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10898.0 (OGCI/catalogue, 327 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10899.0 (OGCI/catalogue, 10 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10900.0 (OGCI/catalogue, 43 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10901.0 (OGCI/catalogue, 32 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10902.0 (OGCI/catalogue, 14 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10903.0 (OGCI/catalogue, 10 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10904.0 (OGCI/catalogue, 12 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10906.0 (OGCI/catalogue, 13 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_10907.0 (OGCI/catalogue, 30 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_11249.0 (OGCI/catalogue, 26 Mt)</t>
+  </si>
+  <si>
+    <t>sto_ogci11250_HRV</t>
+  </si>
+  <si>
+    <t>co2 storage -- ogci_11250.0 (OGCI/catalogue, 15 Mt)</t>
+  </si>
+  <si>
+    <t>PASTI</t>
+  </si>
+  <si>
+    <t>NCAP_COM~CO2</t>
+  </si>
+  <si>
+    <t>ENV_ACT</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>co2_Pula_HRV</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>co2_Split_HRV</t>
+  </si>
+  <si>
+    <t>co2_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>co2s_ogci11250_HRV</t>
   </si>
 </sst>
 </file>
@@ -3274,7 +3641,7 @@
         <v>50</v>
       </c>
       <c r="V28" t="s">
-        <v>399</v>
+        <v>456</v>
       </c>
     </row>
     <row r="29" spans="2:22">
@@ -6100,11 +6467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E304EB98-523F-4B42-9932-94344BF13789}">
-  <dimension ref="B9:AP25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C50DD9-4E38-4635-90D0-ABBAFAF9AFF0}">
+  <dimension ref="B9:BD25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:42">
+    <row r="9" spans="2:56">
       <c r="B9" t="s">
         <v>167</v>
       </c>
@@ -6123,8 +6490,14 @@
       <c r="AL9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="10" spans="2:42">
+      <c r="AR9" t="s">
+        <v>167</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="2:56">
       <c r="B10" t="s">
         <v>168</v>
       </c>
@@ -6233,8 +6606,44 @@
       <c r="AP10" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="11" spans="2:42">
+      <c r="AR10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>169</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>169</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>261</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>209</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>145</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="2:56">
       <c r="B11" t="s">
         <v>175</v>
       </c>
@@ -6296,16 +6705,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99790259024057815</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB11">
-        <v>38.452512256066314</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6335,16 +6744,52 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="AO11">
-        <v>0.99855068763113897</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP11">
-        <v>26.570726762452622</v>
-      </c>
-    </row>
-    <row r="12" spans="2:42">
+        <v>24.858866264948823</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>327</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>349</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>350</v>
+      </c>
+      <c r="BC11">
+        <v>0.99349673079251344</v>
+      </c>
+      <c r="BD11">
+        <v>119.22660213725317</v>
+      </c>
+    </row>
+    <row r="12" spans="2:56">
       <c r="B12" t="s">
         <v>175</v>
       </c>
@@ -6406,16 +6851,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99744104449393167</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB12">
-        <v>46.914184277920093</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6442,19 +6887,55 @@
         <v>280</v>
       </c>
       <c r="AM12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO12">
-        <v>0.99661124612196206</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP12">
-        <v>62.127154430695668</v>
-      </c>
-    </row>
-    <row r="13" spans="2:42">
+        <v>30.912977590144003</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>329</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>330</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>329</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>351</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>268</v>
+      </c>
+      <c r="BC12">
+        <v>0.99748881051271865</v>
+      </c>
+      <c r="BD12">
+        <v>46.038473933492185</v>
+      </c>
+    </row>
+    <row r="13" spans="2:56">
       <c r="B13" t="s">
         <v>175</v>
       </c>
@@ -6516,16 +6997,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99817092025513499</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB13">
-        <v>33.533128655859528</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -6552,10 +7033,10 @@
         <v>282</v>
       </c>
       <c r="AM13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO13">
         <v>0.99806647110300117</v>
@@ -6563,8 +7044,44 @@
       <c r="AP13">
         <v>35.448029778312126</v>
       </c>
-    </row>
-    <row r="14" spans="2:42">
+      <c r="AR13" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>331</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>332</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>331</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>352</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>268</v>
+      </c>
+      <c r="BC13">
+        <v>0.99261900653330459</v>
+      </c>
+      <c r="BD13">
+        <v>135.31821355608193</v>
+      </c>
+    </row>
+    <row r="14" spans="2:56">
       <c r="B14" t="s">
         <v>175</v>
       </c>
@@ -6626,16 +7143,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99608191256693812</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB14">
-        <v>71.831602939467288</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -6662,19 +7179,55 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN14" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="AO14">
-        <v>0.99831383758599213</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP14">
-        <v>30.912977590144003</v>
-      </c>
-    </row>
-    <row r="15" spans="2:42">
+        <v>15.254042454762756</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>333</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>334</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>333</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>353</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>266</v>
+      </c>
+      <c r="BC14">
+        <v>0.99471849364594245</v>
+      </c>
+      <c r="BD14">
+        <v>96.827616491055764</v>
+      </c>
+    </row>
+    <row r="15" spans="2:56">
       <c r="B15" t="s">
         <v>175</v>
       </c>
@@ -6736,16 +7289,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99696148198205803</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB15">
-        <v>55.706163662270022</v>
+        <v>61.639327159526964</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -6775,16 +7328,52 @@
         <v>311</v>
       </c>
       <c r="AN15" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="AO15">
-        <v>0.99868561654722476</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP15">
-        <v>24.097029967546128</v>
-      </c>
-    </row>
-    <row r="16" spans="2:42">
+        <v>26.570726762452622</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>335</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>336</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ15" t="s">
+        <v>335</v>
+      </c>
+      <c r="BA15" t="s">
+        <v>354</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>320</v>
+      </c>
+      <c r="BC15">
+        <v>0.98623672902883308</v>
+      </c>
+      <c r="BD15">
+        <v>252.32663447139444</v>
+      </c>
+    </row>
+    <row r="16" spans="2:56">
       <c r="B16" t="s">
         <v>175</v>
       </c>
@@ -6882,19 +7471,55 @@
         <v>288</v>
       </c>
       <c r="AM16" t="s">
+        <v>312</v>
+      </c>
+      <c r="AN16" t="s">
         <v>313</v>
       </c>
-      <c r="AN16" t="s">
-        <v>266</v>
-      </c>
       <c r="AO16">
-        <v>0.99599733612049879</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP16">
-        <v>73.382171124189711</v>
-      </c>
-    </row>
-    <row r="17" spans="2:42">
+        <v>62.127154430695668</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>337</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>338</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>337</v>
+      </c>
+      <c r="BA16" t="s">
+        <v>355</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>356</v>
+      </c>
+      <c r="BC16">
+        <v>0.99274877595658639</v>
+      </c>
+      <c r="BD16">
+        <v>132.93910746258302</v>
+      </c>
+    </row>
+    <row r="17" spans="2:56">
       <c r="B17" t="s">
         <v>175</v>
       </c>
@@ -6998,13 +7623,49 @@
         <v>315</v>
       </c>
       <c r="AO17">
-        <v>0.99864406184009369</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP17">
-        <v>24.858866264948823</v>
-      </c>
-    </row>
-    <row r="18" spans="2:42">
+        <v>24.097029967546128</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>340</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>339</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>357</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>320</v>
+      </c>
+      <c r="BC17">
+        <v>0.99303722633601399</v>
+      </c>
+      <c r="BD17">
+        <v>127.65085050641102</v>
+      </c>
+    </row>
+    <row r="18" spans="2:56">
       <c r="B18" t="s">
         <v>175</v>
       </c>
@@ -7066,16 +7727,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99752410262804614</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB18">
-        <v>45.391451819153936</v>
+        <v>46.512079711305255</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7105,16 +7766,52 @@
         <v>316</v>
       </c>
       <c r="AN18" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AO18">
-        <v>0.99916796132064933</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP18">
-        <v>15.254042454762756</v>
-      </c>
-    </row>
-    <row r="19" spans="2:42">
+        <v>73.382171124189711</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>341</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>342</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>341</v>
+      </c>
+      <c r="BA18" t="s">
+        <v>358</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>320</v>
+      </c>
+      <c r="BC18">
+        <v>0.99176701066797779</v>
+      </c>
+      <c r="BD18">
+        <v>150.93813775374051</v>
+      </c>
+    </row>
+    <row r="19" spans="2:56">
       <c r="B19" t="s">
         <v>175</v>
       </c>
@@ -7176,16 +7873,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99663785488220757</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB19">
-        <v>61.639327159526964</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7218,13 +7915,49 @@
         <v>318</v>
       </c>
       <c r="AO19">
-        <v>0.99842569630166256</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP19">
-        <v>28.86223446951988</v>
-      </c>
-    </row>
-    <row r="20" spans="2:42">
+        <v>55.559256037121919</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>343</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>344</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>343</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>359</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>305</v>
+      </c>
+      <c r="BC19">
+        <v>0.9956307614354567</v>
+      </c>
+      <c r="BD19">
+        <v>80.102707016626312</v>
+      </c>
+    </row>
+    <row r="20" spans="2:56">
       <c r="B20" t="s">
         <v>175</v>
       </c>
@@ -7286,16 +8019,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99841413454839123</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB20">
-        <v>29.074199946161183</v>
+        <v>24.321425308170515</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -7333,8 +8066,44 @@
       <c r="AP20">
         <v>126.6592518997923</v>
       </c>
-    </row>
-    <row r="21" spans="2:42">
+      <c r="AR20" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>345</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>346</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ20" t="s">
+        <v>345</v>
+      </c>
+      <c r="BA20" t="s">
+        <v>360</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>268</v>
+      </c>
+      <c r="BC20">
+        <v>0.9950151616455658</v>
+      </c>
+      <c r="BD20">
+        <v>91.388703164627643</v>
+      </c>
+    </row>
+    <row r="21" spans="2:56">
       <c r="B21" t="s">
         <v>175</v>
       </c>
@@ -7396,16 +8165,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99606139674621874</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB21">
-        <v>72.207726319322958</v>
+        <v>22.196688250206851</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -7438,13 +8207,49 @@
         <v>322</v>
       </c>
       <c r="AO21">
-        <v>0.99696949512524791</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP21">
-        <v>55.559256037121919</v>
-      </c>
-    </row>
-    <row r="22" spans="2:42">
+        <v>28.86223446951988</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>347</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>348</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>179</v>
+      </c>
+      <c r="AZ21" t="s">
+        <v>347</v>
+      </c>
+      <c r="BA21" t="s">
+        <v>361</v>
+      </c>
+      <c r="BB21" t="s">
+        <v>320</v>
+      </c>
+      <c r="BC21">
+        <v>0.99654308092357613</v>
+      </c>
+      <c r="BD21">
+        <v>63.376849734436668</v>
+      </c>
+    </row>
+    <row r="22" spans="2:56">
       <c r="B22" t="s">
         <v>175</v>
       </c>
@@ -7506,16 +8311,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99867337680137247</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB22">
-        <v>24.321425308170515</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -7554,7 +8359,7 @@
         <v>38.436805513593036</v>
       </c>
     </row>
-    <row r="23" spans="2:42">
+    <row r="23" spans="2:56">
       <c r="B23" t="s">
         <v>175</v>
       </c>
@@ -7616,16 +8421,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99878927154998876</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB23">
-        <v>22.196688250206851</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -7664,7 +8469,7 @@
         <v>30.913284433006623</v>
       </c>
     </row>
-    <row r="24" spans="2:42">
+    <row r="24" spans="2:56">
       <c r="B24" t="s">
         <v>175</v>
       </c>
@@ -7726,19 +8531,19 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99833598914935617</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB24">
-        <v>30.506865595137178</v>
-      </c>
-    </row>
-    <row r="25" spans="2:42">
+        <v>71.831602939467288</v>
+      </c>
+    </row>
+    <row r="25" spans="2:56">
       <c r="B25" t="s">
         <v>175</v>
       </c>
@@ -7800,16 +8605,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99746297747029244</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB25">
-        <v>46.512079711305255</v>
+        <v>55.706163662270022</v>
       </c>
     </row>
   </sheetData>
@@ -7818,19 +8623,25 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E4E7B2-2305-4E3D-A8E9-9AC35F65F775}">
-  <dimension ref="B9:M23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB73AA55-1319-4E16-9823-8E5F3816DB39}">
+  <dimension ref="B9:Z23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:26">
       <c r="B9" t="s">
         <v>167</v>
       </c>
       <c r="J9" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="10" spans="2:13">
+      <c r="O9" t="s">
+        <v>167</v>
+      </c>
+      <c r="W9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26">
       <c r="B10" t="s">
         <v>168</v>
       </c>
@@ -7864,16 +8675,49 @@
       <c r="M10" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="11" spans="2:13">
+      <c r="O10" t="s">
+        <v>168</v>
+      </c>
+      <c r="P10" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>170</v>
+      </c>
+      <c r="R10" t="s">
+        <v>171</v>
+      </c>
+      <c r="S10" t="s">
+        <v>172</v>
+      </c>
+      <c r="T10" t="s">
+        <v>173</v>
+      </c>
+      <c r="U10" t="s">
+        <v>174</v>
+      </c>
+      <c r="W10" t="s">
+        <v>169</v>
+      </c>
+      <c r="X10" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
       <c r="B11" t="s">
         <v>175</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="D11" t="s">
-        <v>328</v>
+        <v>363</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7888,7 +8732,7 @@
         <v>179</v>
       </c>
       <c r="J11" t="s">
-        <v>327</v>
+        <v>362</v>
       </c>
       <c r="K11" t="s">
         <v>319</v>
@@ -7899,16 +8743,49 @@
       <c r="M11">
         <v>0.15405786738589439</v>
       </c>
-    </row>
-    <row r="12" spans="2:13">
+      <c r="O11" t="s">
+        <v>175</v>
+      </c>
+      <c r="P11" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>389</v>
+      </c>
+      <c r="R11" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" t="s">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s">
+        <v>178</v>
+      </c>
+      <c r="U11" t="s">
+        <v>179</v>
+      </c>
+      <c r="W11" t="s">
+        <v>388</v>
+      </c>
+      <c r="X11" t="s">
+        <v>353</v>
+      </c>
+      <c r="Y11">
+        <v>4.1159999999999997</v>
+      </c>
+      <c r="Z11">
+        <v>0.22250011702003011</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
       <c r="B12" t="s">
         <v>175</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="D12" t="s">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -7923,10 +8800,10 @@
         <v>179</v>
       </c>
       <c r="J12" t="s">
-        <v>329</v>
+        <v>364</v>
       </c>
       <c r="K12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -7934,16 +8811,49 @@
       <c r="M12">
         <v>0.1702258774374108</v>
       </c>
-    </row>
-    <row r="13" spans="2:13">
+      <c r="O12" t="s">
+        <v>175</v>
+      </c>
+      <c r="P12" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>391</v>
+      </c>
+      <c r="R12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" t="s">
+        <v>21</v>
+      </c>
+      <c r="T12" t="s">
+        <v>178</v>
+      </c>
+      <c r="U12" t="s">
+        <v>179</v>
+      </c>
+      <c r="W12" t="s">
+        <v>390</v>
+      </c>
+      <c r="X12" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y12">
+        <v>13.587</v>
+      </c>
+      <c r="Z12">
+        <v>0.28183868578249072</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26">
       <c r="B13" t="s">
         <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="D13" t="s">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -7958,7 +8868,7 @@
         <v>179</v>
       </c>
       <c r="J13" t="s">
-        <v>331</v>
+        <v>366</v>
       </c>
       <c r="K13" t="s">
         <v>323</v>
@@ -7969,16 +8879,49 @@
       <c r="M13">
         <v>0.2114500856672481</v>
       </c>
-    </row>
-    <row r="14" spans="2:13">
+      <c r="O13" t="s">
+        <v>175</v>
+      </c>
+      <c r="P13" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>393</v>
+      </c>
+      <c r="R13" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" t="s">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s">
+        <v>178</v>
+      </c>
+      <c r="U13" t="s">
+        <v>179</v>
+      </c>
+      <c r="W13" t="s">
+        <v>392</v>
+      </c>
+      <c r="X13" t="s">
+        <v>354</v>
+      </c>
+      <c r="Y13">
+        <v>2.415</v>
+      </c>
+      <c r="Z13">
+        <v>0.25164529554790871</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
       <c r="B14" t="s">
         <v>175</v>
       </c>
       <c r="C14" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="D14" t="s">
-        <v>334</v>
+        <v>369</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -7993,10 +8936,10 @@
         <v>179</v>
       </c>
       <c r="J14" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="K14" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8004,16 +8947,49 @@
       <c r="M14">
         <v>0.108408181125487</v>
       </c>
-    </row>
-    <row r="15" spans="2:13">
+      <c r="O14" t="s">
+        <v>175</v>
+      </c>
+      <c r="P14" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>395</v>
+      </c>
+      <c r="R14" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>178</v>
+      </c>
+      <c r="U14" t="s">
+        <v>179</v>
+      </c>
+      <c r="W14" t="s">
+        <v>394</v>
+      </c>
+      <c r="X14" t="s">
+        <v>358</v>
+      </c>
+      <c r="Y14">
+        <v>6.5782499999999997</v>
+      </c>
+      <c r="Z14">
+        <v>0.26921565612439891</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
       <c r="B15" t="s">
         <v>175</v>
       </c>
       <c r="C15" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="D15" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -8028,10 +9004,10 @@
         <v>179</v>
       </c>
       <c r="J15" t="s">
-        <v>335</v>
+        <v>370</v>
       </c>
       <c r="K15" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -8039,16 +9015,49 @@
       <c r="M15">
         <v>0.19141286458792939</v>
       </c>
-    </row>
-    <row r="16" spans="2:13">
+      <c r="O15" t="s">
+        <v>175</v>
+      </c>
+      <c r="P15" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>397</v>
+      </c>
+      <c r="R15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s">
+        <v>178</v>
+      </c>
+      <c r="U15" t="s">
+        <v>179</v>
+      </c>
+      <c r="W15" t="s">
+        <v>396</v>
+      </c>
+      <c r="X15" t="s">
+        <v>355</v>
+      </c>
+      <c r="Y15">
+        <v>9.5145</v>
+      </c>
+      <c r="Z15">
+        <v>0.22810819291996931</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
       <c r="B16" t="s">
         <v>175</v>
       </c>
       <c r="C16" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="D16" t="s">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -8063,10 +9072,10 @@
         <v>179</v>
       </c>
       <c r="J16" t="s">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="K16" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -8074,16 +9083,49 @@
       <c r="M16">
         <v>0.10174329649985191</v>
       </c>
-    </row>
-    <row r="17" spans="2:13">
+      <c r="O16" t="s">
+        <v>175</v>
+      </c>
+      <c r="P16" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>399</v>
+      </c>
+      <c r="R16" t="s">
+        <v>10</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>178</v>
+      </c>
+      <c r="U16" t="s">
+        <v>179</v>
+      </c>
+      <c r="W16" t="s">
+        <v>398</v>
+      </c>
+      <c r="X16" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y16">
+        <v>13.50075</v>
+      </c>
+      <c r="Z16">
+        <v>0.25802981712533229</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26">
       <c r="B17" t="s">
         <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="D17" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -8098,10 +9140,10 @@
         <v>179</v>
       </c>
       <c r="J17" t="s">
-        <v>339</v>
+        <v>374</v>
       </c>
       <c r="K17" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -8109,16 +9151,49 @@
       <c r="M17">
         <v>0.1251653949323632</v>
       </c>
-    </row>
-    <row r="18" spans="2:13">
+      <c r="O17" t="s">
+        <v>175</v>
+      </c>
+      <c r="P17" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>401</v>
+      </c>
+      <c r="R17" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s">
+        <v>178</v>
+      </c>
+      <c r="U17" t="s">
+        <v>179</v>
+      </c>
+      <c r="W17" t="s">
+        <v>400</v>
+      </c>
+      <c r="X17" t="s">
+        <v>351</v>
+      </c>
+      <c r="Y17">
+        <v>5.1029999999999998</v>
+      </c>
+      <c r="Z17">
+        <v>0.22842178935178781</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26">
       <c r="B18" t="s">
         <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="D18" t="s">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -8133,7 +9208,7 @@
         <v>179</v>
       </c>
       <c r="J18" t="s">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="K18" t="s">
         <v>325</v>
@@ -8144,16 +9219,49 @@
       <c r="M18">
         <v>0.1142138251233057</v>
       </c>
-    </row>
-    <row r="19" spans="2:13">
+      <c r="O18" t="s">
+        <v>175</v>
+      </c>
+      <c r="P18" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>403</v>
+      </c>
+      <c r="R18" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" t="s">
+        <v>178</v>
+      </c>
+      <c r="U18" t="s">
+        <v>179</v>
+      </c>
+      <c r="W18" t="s">
+        <v>402</v>
+      </c>
+      <c r="X18" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y18">
+        <v>6.9870000000000001</v>
+      </c>
+      <c r="Z18">
+        <v>0.25667420307192768</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26">
       <c r="B19" t="s">
         <v>175</v>
       </c>
       <c r="C19" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
       <c r="D19" t="s">
-        <v>344</v>
+        <v>379</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -8168,10 +9276,10 @@
         <v>179</v>
       </c>
       <c r="J19" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
       <c r="K19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -8179,16 +9287,49 @@
       <c r="M19">
         <v>0.14779915155023299</v>
       </c>
-    </row>
-    <row r="20" spans="2:13">
+      <c r="O19" t="s">
+        <v>175</v>
+      </c>
+      <c r="P19" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>405</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>21</v>
+      </c>
+      <c r="T19" t="s">
+        <v>178</v>
+      </c>
+      <c r="U19" t="s">
+        <v>179</v>
+      </c>
+      <c r="W19" t="s">
+        <v>404</v>
+      </c>
+      <c r="X19" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y19">
+        <v>5.6325000000000003</v>
+      </c>
+      <c r="Z19">
+        <v>0.24267344854691961</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
       <c r="B20" t="s">
         <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="D20" t="s">
-        <v>346</v>
+        <v>381</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -8203,10 +9344,10 @@
         <v>179</v>
       </c>
       <c r="J20" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
       <c r="K20" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -8214,16 +9355,49 @@
       <c r="M20">
         <v>0.11030030335467821</v>
       </c>
-    </row>
-    <row r="21" spans="2:13">
+      <c r="O20" t="s">
+        <v>175</v>
+      </c>
+      <c r="P20" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>407</v>
+      </c>
+      <c r="R20" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" t="s">
+        <v>178</v>
+      </c>
+      <c r="U20" t="s">
+        <v>179</v>
+      </c>
+      <c r="W20" t="s">
+        <v>406</v>
+      </c>
+      <c r="X20" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y20">
+        <v>9.4177499999999998</v>
+      </c>
+      <c r="Z20">
+        <v>0.2484180500672426</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26">
       <c r="B21" t="s">
         <v>175</v>
       </c>
       <c r="C21" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="D21" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -8238,10 +9412,10 @@
         <v>179</v>
       </c>
       <c r="J21" t="s">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="K21" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -8249,16 +9423,49 @@
       <c r="M21">
         <v>0.1169364698808104</v>
       </c>
-    </row>
-    <row r="22" spans="2:13">
+      <c r="O21" t="s">
+        <v>175</v>
+      </c>
+      <c r="P21" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>409</v>
+      </c>
+      <c r="R21" t="s">
+        <v>10</v>
+      </c>
+      <c r="S21" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s">
+        <v>178</v>
+      </c>
+      <c r="U21" t="s">
+        <v>179</v>
+      </c>
+      <c r="W21" t="s">
+        <v>408</v>
+      </c>
+      <c r="X21" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y21">
+        <v>7.4775</v>
+      </c>
+      <c r="Z21">
+        <v>0.26608294067043042</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
       <c r="B22" t="s">
         <v>175</v>
       </c>
       <c r="C22" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="D22" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -8273,10 +9480,10 @@
         <v>179</v>
       </c>
       <c r="J22" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="K22" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -8285,15 +9492,15 @@
         <v>0.18255280698994311</v>
       </c>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:26">
       <c r="B23" t="s">
         <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="D23" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -8308,10 +9515,10 @@
         <v>179</v>
       </c>
       <c r="J23" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="K23" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -8326,13 +9533,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0F46F0-1E13-478C-AF55-7CA9C08BED4B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711220C6-5BD3-4303-8CAE-DB174FB160E2}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:21">
       <c r="B9" t="s">
-        <v>353</v>
+        <v>410</v>
       </c>
       <c r="O9" t="s">
         <v>167</v>
@@ -8399,7 +9606,7 @@
     </row>
     <row r="11" spans="2:21">
       <c r="B11" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -8417,13 +9624,13 @@
         <v>941</v>
       </c>
       <c r="M11" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="O11" t="s">
         <v>175</v>
       </c>
       <c r="P11" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -8435,12 +9642,12 @@
         <v>232</v>
       </c>
       <c r="U11" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="2:21">
       <c r="B12" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -8458,13 +9665,13 @@
         <v>23.5</v>
       </c>
       <c r="M12" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="O12" t="s">
         <v>175</v>
       </c>
       <c r="P12" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -8476,12 +9683,12 @@
         <v>232</v>
       </c>
       <c r="U12" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="2:21">
       <c r="B13" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -8499,13 +9706,13 @@
         <v>0.497</v>
       </c>
       <c r="M13" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="O13" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="P13" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -8517,12 +9724,12 @@
         <v>232</v>
       </c>
       <c r="U13" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="2:21">
       <c r="B14" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -8546,7 +9753,7 @@
         <v>175</v>
       </c>
       <c r="P14" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -8558,12 +9765,12 @@
         <v>232</v>
       </c>
       <c r="U14" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="2:21">
       <c r="B15" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -8596,13 +9803,13 @@
         <v>30</v>
       </c>
       <c r="M15" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="O15" t="s">
         <v>175</v>
       </c>
       <c r="P15" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -8614,12 +9821,12 @@
         <v>232</v>
       </c>
       <c r="U15" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="2:21">
       <c r="B16" t="s">
-        <v>354</v>
+        <v>411</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -8652,13 +9859,13 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="O16" t="s">
         <v>175</v>
       </c>
       <c r="P16" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -8670,12 +9877,12 @@
         <v>232</v>
       </c>
       <c r="U16" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="2:21">
       <c r="B17" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -8693,13 +9900,13 @@
         <v>470.5</v>
       </c>
       <c r="M17" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="O17" t="s">
         <v>175</v>
       </c>
       <c r="P17" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -8711,12 +9918,12 @@
         <v>232</v>
       </c>
       <c r="U17" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18" spans="2:21">
       <c r="B18" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -8734,13 +9941,13 @@
         <v>18.8</v>
       </c>
       <c r="M18" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="O18" t="s">
         <v>175</v>
       </c>
       <c r="P18" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -8752,12 +9959,12 @@
         <v>232</v>
       </c>
       <c r="U18" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" spans="2:21">
       <c r="B19" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -8775,13 +9982,13 @@
         <v>1.9279999999999999</v>
       </c>
       <c r="M19" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="O19" t="s">
         <v>175</v>
       </c>
       <c r="P19" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -8793,12 +10000,12 @@
         <v>232</v>
       </c>
       <c r="U19" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" spans="2:21">
       <c r="B20" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
@@ -8822,7 +10029,7 @@
         <v>175</v>
       </c>
       <c r="P20" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -8834,12 +10041,12 @@
         <v>232</v>
       </c>
       <c r="U20" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="21" spans="2:21">
       <c r="B21" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -8872,13 +10079,13 @@
         <v>30</v>
       </c>
       <c r="M21" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="O21" t="s">
         <v>175</v>
       </c>
       <c r="P21" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -8890,12 +10097,12 @@
         <v>232</v>
       </c>
       <c r="U21" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="2:21">
       <c r="B22" t="s">
-        <v>360</v>
+        <v>417</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -8928,13 +10135,13 @@
         <v>2</v>
       </c>
       <c r="M22" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
       <c r="O22" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="P22" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -8946,18 +10153,18 @@
         <v>232</v>
       </c>
       <c r="U22" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" spans="2:21">
       <c r="B23" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E23">
         <v>967.6</v>
@@ -8969,13 +10176,13 @@
         <v>879.6</v>
       </c>
       <c r="M23" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
       <c r="O23" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="P23" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -8984,21 +10191,21 @@
         <v>21</v>
       </c>
       <c r="T23" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="U23" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="2:21">
       <c r="B24" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E24">
         <v>32.200000000000003</v>
@@ -9010,13 +10217,13 @@
         <v>28.6</v>
       </c>
       <c r="M24" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
       <c r="O24" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="P24" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -9025,21 +10232,21 @@
         <v>21</v>
       </c>
       <c r="T24" t="s">
-        <v>385</v>
+        <v>442</v>
       </c>
       <c r="U24" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="2:21">
       <c r="B25" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E25">
         <v>1.3</v>
@@ -9051,13 +10258,13 @@
         <v>1.2</v>
       </c>
       <c r="M25" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
       <c r="O25" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="P25" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -9069,18 +10276,18 @@
         <v>232</v>
       </c>
       <c r="U25" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="2:21">
       <c r="B26" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E26">
         <v>0.56000000000000005</v>
@@ -9095,10 +10302,10 @@
         <v>145</v>
       </c>
       <c r="O26" t="s">
-        <v>384</v>
+        <v>441</v>
       </c>
       <c r="P26" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -9110,18 +10317,18 @@
         <v>232</v>
       </c>
       <c r="U26" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" spans="2:21">
       <c r="B27" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -9148,13 +10355,13 @@
         <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
       <c r="O27" t="s">
-        <v>383</v>
+        <v>440</v>
       </c>
       <c r="P27" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -9166,18 +10373,18 @@
         <v>232</v>
       </c>
       <c r="U27" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
     </row>
     <row r="28" spans="2:21">
       <c r="B28" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -9204,18 +10411,18 @@
         <v>3</v>
       </c>
       <c r="M28" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="2:21">
       <c r="B29" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E29">
         <v>0.55559999999999998</v>
@@ -9227,18 +10434,18 @@
         <v>0.45450000000000002</v>
       </c>
       <c r="M29" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="2:21">
       <c r="B30" t="s">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E30">
         <v>0.15</v>
@@ -9250,18 +10457,18 @@
         <v>0.15</v>
       </c>
       <c r="M30" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
     </row>
     <row r="31" spans="2:21">
       <c r="B31" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
       </c>
       <c r="D31" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="F31">
         <v>2917</v>
@@ -9273,18 +10480,18 @@
         <v>2446.5</v>
       </c>
       <c r="M31" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="32" spans="2:21">
       <c r="B32" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
       </c>
       <c r="D32" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="F32">
         <v>70.599999999999994</v>
@@ -9296,18 +10503,18 @@
         <v>61.2</v>
       </c>
       <c r="M32" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="33" spans="2:13">
       <c r="B33" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C33" t="s">
         <v>33</v>
       </c>
       <c r="D33" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="F33">
         <v>1.294</v>
@@ -9319,18 +10526,18 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="M33" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="34" spans="2:13">
       <c r="B34" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C34" t="s">
         <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="F34">
         <v>0.52</v>
@@ -9347,13 +10554,13 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E35">
         <v>30</v>
@@ -9380,18 +10587,18 @@
         <v>30</v>
       </c>
       <c r="M35" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>366</v>
+        <v>423</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -9418,12 +10625,12 @@
         <v>4</v>
       </c>
       <c r="M36" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="2:13">
       <c r="B37" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C37" t="s">
         <v>32</v>
@@ -9441,12 +10648,12 @@
         <v>1599.6</v>
       </c>
       <c r="M37" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" spans="2:13">
       <c r="B38" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
@@ -9464,12 +10671,12 @@
         <v>42.3</v>
       </c>
       <c r="M38" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" spans="2:13">
       <c r="B39" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
@@ -9487,12 +10694,12 @@
         <v>2.3610000000000002</v>
       </c>
       <c r="M39" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="2:13">
       <c r="B40" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
@@ -9515,7 +10722,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -9548,12 +10755,12 @@
         <v>40</v>
       </c>
       <c r="M41" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="2:13">
       <c r="B42" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -9586,12 +10793,12 @@
         <v>4</v>
       </c>
       <c r="M42" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="2:13">
       <c r="B43" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -9609,12 +10816,12 @@
         <v>1881.9</v>
       </c>
       <c r="M43" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="44" spans="2:13">
       <c r="B44" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -9632,12 +10839,12 @@
         <v>56.5</v>
       </c>
       <c r="M44" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="45" spans="2:13">
       <c r="B45" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -9655,12 +10862,12 @@
         <v>2.3170000000000002</v>
       </c>
       <c r="M45" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" spans="2:13">
       <c r="B46" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
@@ -9683,7 +10890,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -9716,12 +10923,12 @@
         <v>40</v>
       </c>
       <c r="M47" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="48" spans="2:13">
       <c r="B48" t="s">
-        <v>368</v>
+        <v>425</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -9754,12 +10961,12 @@
         <v>4</v>
       </c>
       <c r="M48" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="2:13">
       <c r="B49" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -9777,12 +10984,12 @@
         <v>2070.1</v>
       </c>
       <c r="M49" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="50" spans="2:13">
       <c r="B50" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
@@ -9800,12 +11007,12 @@
         <v>61.2</v>
       </c>
       <c r="M50" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
@@ -9823,12 +11030,12 @@
         <v>2.6389999999999998</v>
       </c>
       <c r="M51" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" spans="2:13">
       <c r="B52" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
@@ -9851,7 +11058,7 @@
     </row>
     <row r="53" spans="2:13">
       <c r="B53" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
@@ -9884,12 +11091,12 @@
         <v>40</v>
       </c>
       <c r="M53" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" spans="2:13">
       <c r="B54" t="s">
-        <v>369</v>
+        <v>426</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
@@ -9922,12 +11129,12 @@
         <v>4</v>
       </c>
       <c r="M54" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -9945,12 +11152,12 @@
         <v>2164.1999999999998</v>
       </c>
       <c r="M55" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56" spans="2:13">
       <c r="B56" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -9968,12 +11175,12 @@
         <v>75.3</v>
       </c>
       <c r="M56" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="2:13">
       <c r="B57" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -9996,7 +11203,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -10029,12 +11236,12 @@
         <v>40</v>
       </c>
       <c r="M58" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="59" spans="2:13">
       <c r="B59" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -10067,12 +11274,12 @@
         <v>4</v>
       </c>
       <c r="M59" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="2:13">
       <c r="B60" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C60" t="s">
         <v>36</v>
@@ -10090,12 +11297,12 @@
         <v>4234.3</v>
       </c>
       <c r="M60" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
@@ -10113,12 +11320,12 @@
         <v>150.6</v>
       </c>
       <c r="M61" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="2:13">
       <c r="B62" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
@@ -10133,12 +11340,12 @@
         <v>0.77800000000000002</v>
       </c>
       <c r="M62" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="63" spans="2:13">
       <c r="B63" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C63" t="s">
         <v>36</v>
@@ -10171,12 +11378,12 @@
         <v>60</v>
       </c>
       <c r="M63" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="64" spans="2:13">
       <c r="B64" t="s">
-        <v>371</v>
+        <v>428</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
@@ -10209,12 +11416,12 @@
         <v>7</v>
       </c>
       <c r="M64" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="2:13">
       <c r="B65" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="C65" t="s">
         <v>36</v>
@@ -10238,12 +11445,12 @@
         <v>4884.6000000000004</v>
       </c>
       <c r="M65" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="66" spans="2:13">
       <c r="B66" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="C66" t="s">
         <v>36</v>
@@ -10267,12 +11474,12 @@
         <v>136</v>
       </c>
       <c r="M66" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="67" spans="2:13">
       <c r="B67" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
@@ -10296,12 +11503,12 @@
         <v>0.72199999999999998</v>
       </c>
       <c r="M67" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="68" spans="2:13">
       <c r="B68" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="C68" t="s">
         <v>36</v>
@@ -10334,12 +11541,12 @@
         <v>40</v>
       </c>
       <c r="M68" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="69" spans="2:13">
       <c r="B69" t="s">
-        <v>372</v>
+        <v>429</v>
       </c>
       <c r="C69" t="s">
         <v>36</v>
@@ -10372,12 +11579,12 @@
         <v>3</v>
       </c>
       <c r="M69" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="70" spans="2:13">
       <c r="B70" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C70" t="s">
         <v>31</v>
@@ -10395,12 +11602,12 @@
         <v>2164.1999999999998</v>
       </c>
       <c r="M70" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="71" spans="2:13">
       <c r="B71" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C71" t="s">
         <v>31</v>
@@ -10418,12 +11625,12 @@
         <v>75.3</v>
       </c>
       <c r="M71" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72" spans="2:13">
       <c r="B72" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C72" t="s">
         <v>31</v>
@@ -10441,12 +11648,12 @@
         <v>1.4570000000000001</v>
       </c>
       <c r="M72" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="73" spans="2:13">
       <c r="B73" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C73" t="s">
         <v>31</v>
@@ -10469,7 +11676,7 @@
     </row>
     <row r="74" spans="2:13">
       <c r="B74" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C74" t="s">
         <v>31</v>
@@ -10487,12 +11694,12 @@
         <v>0.6</v>
       </c>
       <c r="M74" t="s">
-        <v>374</v>
+        <v>431</v>
       </c>
     </row>
     <row r="75" spans="2:13">
       <c r="B75" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C75" t="s">
         <v>31</v>
@@ -10525,12 +11732,12 @@
         <v>45</v>
       </c>
       <c r="M75" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" t="s">
-        <v>373</v>
+        <v>430</v>
       </c>
       <c r="C76" t="s">
         <v>31</v>
@@ -10563,18 +11770,18 @@
         <v>3</v>
       </c>
       <c r="M76" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="77" spans="2:13">
       <c r="B77" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
       </c>
       <c r="D77" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E77">
         <v>2748.9</v>
@@ -10586,18 +11793,18 @@
         <v>2528.9</v>
       </c>
       <c r="M77" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C78" t="s">
         <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E78">
         <v>75.900000000000006</v>
@@ -10609,18 +11816,18 @@
         <v>68.2</v>
       </c>
       <c r="M78" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C79" t="s">
         <v>31</v>
       </c>
       <c r="D79" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E79">
         <v>0.8</v>
@@ -10632,18 +11839,18 @@
         <v>0.8</v>
       </c>
       <c r="M79" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="80" spans="2:13">
       <c r="B80" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C80" t="s">
         <v>31</v>
       </c>
       <c r="D80" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E80">
         <v>0.40899999999999997</v>
@@ -10660,13 +11867,13 @@
     </row>
     <row r="81" spans="2:13">
       <c r="B81" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C81" t="s">
         <v>31</v>
       </c>
       <c r="D81" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E81">
         <v>25</v>
@@ -10693,18 +11900,18 @@
         <v>25</v>
       </c>
       <c r="M81" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="82" spans="2:13">
       <c r="B82" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C82" t="s">
         <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E82">
         <v>2</v>
@@ -10731,18 +11938,18 @@
         <v>2</v>
       </c>
       <c r="M82" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="83" spans="2:13">
       <c r="B83" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C83" t="s">
         <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E83">
         <v>1.8237000000000001</v>
@@ -10754,18 +11961,18 @@
         <v>1.9169</v>
       </c>
       <c r="M83" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" spans="2:13">
       <c r="B84" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="C84" t="s">
         <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E84">
         <v>0.14000000000000001</v>
@@ -10777,18 +11984,18 @@
         <v>0.13</v>
       </c>
       <c r="M84" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
     </row>
     <row r="85" spans="2:13">
       <c r="B85" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C85" t="s">
         <v>33</v>
       </c>
       <c r="D85" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E85">
         <v>66</v>
@@ -10800,18 +12007,18 @@
         <v>55</v>
       </c>
       <c r="M85" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="86" spans="2:13">
       <c r="B86" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C86" t="s">
         <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E86">
         <v>2.1</v>
@@ -10823,18 +12030,18 @@
         <v>1.9</v>
       </c>
       <c r="M86" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="87" spans="2:13">
       <c r="B87" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C87" t="s">
         <v>33</v>
       </c>
       <c r="D87" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E87">
         <v>0.3</v>
@@ -10846,18 +12053,18 @@
         <v>0.3</v>
       </c>
       <c r="M87" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="88" spans="2:13">
       <c r="B88" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C88" t="s">
         <v>33</v>
       </c>
       <c r="D88" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E88">
         <v>1.03</v>
@@ -10874,13 +12081,13 @@
     </row>
     <row r="89" spans="2:13">
       <c r="B89" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C89" t="s">
         <v>33</v>
       </c>
       <c r="D89" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E89">
         <v>25</v>
@@ -10907,18 +12114,18 @@
         <v>25</v>
       </c>
       <c r="M89" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="90" spans="2:13">
       <c r="B90" t="s">
-        <v>376</v>
+        <v>433</v>
       </c>
       <c r="C90" t="s">
         <v>33</v>
       </c>
       <c r="D90" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -10945,18 +12152,18 @@
         <v>1</v>
       </c>
       <c r="M90" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="91" spans="2:13">
       <c r="B91" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C91" t="s">
         <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E91">
         <v>483.8</v>
@@ -10968,18 +12175,18 @@
         <v>439.8</v>
       </c>
       <c r="M91" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="92" spans="2:13">
       <c r="B92" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C92" t="s">
         <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E92">
         <v>38</v>
@@ -10991,18 +12198,18 @@
         <v>34.5</v>
       </c>
       <c r="M92" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="93" spans="2:13">
       <c r="B93" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E93">
         <v>0.4</v>
@@ -11014,18 +12221,18 @@
         <v>0.4</v>
       </c>
       <c r="M93" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" spans="2:13">
       <c r="B94" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E94">
         <v>1.149</v>
@@ -11042,13 +12249,13 @@
     </row>
     <row r="95" spans="2:13">
       <c r="B95" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E95">
         <v>25</v>
@@ -11075,18 +12282,18 @@
         <v>25</v>
       </c>
       <c r="M95" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="96" spans="2:13">
       <c r="B96" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
       </c>
       <c r="D96" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -11113,18 +12320,18 @@
         <v>3</v>
       </c>
       <c r="M96" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="97" spans="2:13">
       <c r="B97" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C97" t="s">
         <v>19</v>
       </c>
       <c r="D97" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G97">
         <v>72.400000000000006</v>
@@ -11142,18 +12349,18 @@
         <v>72.400000000000006</v>
       </c>
       <c r="M97" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="98" spans="2:13">
       <c r="B98" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C98" t="s">
         <v>19</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G98">
         <v>1.2</v>
@@ -11171,18 +12378,18 @@
         <v>1.2</v>
       </c>
       <c r="M98" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="99" spans="2:13">
       <c r="B99" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C99" t="s">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G99">
         <v>0.2</v>
@@ -11200,18 +12407,18 @@
         <v>0.2</v>
       </c>
       <c r="M99" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="100" spans="2:13">
       <c r="B100" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C100" t="s">
         <v>19</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G100">
         <v>0.99</v>
@@ -11234,13 +12441,13 @@
     </row>
     <row r="101" spans="2:13">
       <c r="B101" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C101" t="s">
         <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E101">
         <v>20</v>
@@ -11267,18 +12474,18 @@
         <v>20</v>
       </c>
       <c r="M101" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="102" spans="2:13">
       <c r="B102" t="s">
-        <v>378</v>
+        <v>435</v>
       </c>
       <c r="C102" t="s">
         <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -11305,18 +12512,18 @@
         <v>1</v>
       </c>
       <c r="M102" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="103" spans="2:13">
       <c r="B103" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C103" t="s">
         <v>19</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G103">
         <v>1054.7</v>
@@ -11334,18 +12541,18 @@
         <v>951.9</v>
       </c>
       <c r="M103" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="2:13">
       <c r="B104" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C104" t="s">
         <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G104">
         <v>2.2000000000000002</v>
@@ -11363,18 +12570,18 @@
         <v>2</v>
       </c>
       <c r="M104" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="105" spans="2:13">
       <c r="B105" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C105" t="s">
         <v>19</v>
       </c>
       <c r="D105" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G105">
         <v>0.2</v>
@@ -11392,18 +12599,18 @@
         <v>0.2</v>
       </c>
       <c r="M105" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C106" t="s">
         <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="G106">
         <v>2.8</v>
@@ -11426,13 +12633,13 @@
     </row>
     <row r="107" spans="2:13">
       <c r="B107" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C107" t="s">
         <v>19</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E107">
         <v>25</v>
@@ -11459,18 +12666,18 @@
         <v>25</v>
       </c>
       <c r="M107" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" t="s">
-        <v>379</v>
+        <v>436</v>
       </c>
       <c r="C108" t="s">
         <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>419</v>
       </c>
       <c r="E108">
         <v>1</v>
@@ -11497,18 +12704,18 @@
         <v>1</v>
       </c>
       <c r="M108" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C109" t="s">
         <v>33</v>
       </c>
       <c r="D109" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E109">
         <v>0.52</v>
@@ -11540,13 +12747,13 @@
     </row>
     <row r="110" spans="2:13">
       <c r="B110" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C110" t="s">
         <v>33</v>
       </c>
       <c r="D110" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E110">
         <v>2917</v>
@@ -11573,18 +12780,18 @@
         <v>2917</v>
       </c>
       <c r="M110" t="s">
-        <v>355</v>
+        <v>412</v>
       </c>
     </row>
     <row r="111" spans="2:13">
       <c r="B111" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C111" t="s">
         <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E111">
         <v>70.599999999999994</v>
@@ -11611,18 +12818,18 @@
         <v>70.599999999999994</v>
       </c>
       <c r="M111" t="s">
-        <v>356</v>
+        <v>413</v>
       </c>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C112" t="s">
         <v>33</v>
       </c>
       <c r="D112" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E112">
         <v>1.3</v>
@@ -11649,18 +12856,18 @@
         <v>1.3</v>
       </c>
       <c r="M112" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="113" spans="2:13">
       <c r="B113" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E113">
         <v>0.55559999999999998</v>
@@ -11687,18 +12894,18 @@
         <v>0.55559999999999998</v>
       </c>
       <c r="M113" t="s">
-        <v>363</v>
+        <v>420</v>
       </c>
     </row>
     <row r="114" spans="2:13">
       <c r="B114" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C114" t="s">
         <v>33</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E114">
         <v>0.15</v>
@@ -11725,18 +12932,18 @@
         <v>0.15</v>
       </c>
       <c r="M114" t="s">
-        <v>364</v>
+        <v>421</v>
       </c>
     </row>
     <row r="115" spans="2:13">
       <c r="B115" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C115" t="s">
         <v>33</v>
       </c>
       <c r="D115" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E115">
         <v>25</v>
@@ -11763,18 +12970,18 @@
         <v>25</v>
       </c>
       <c r="M115" t="s">
-        <v>358</v>
+        <v>415</v>
       </c>
     </row>
     <row r="116" spans="2:13">
       <c r="B116" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C116" t="s">
         <v>33</v>
       </c>
       <c r="D116" t="s">
-        <v>381</v>
+        <v>438</v>
       </c>
       <c r="E116">
         <v>4</v>
@@ -11801,7 +13008,7 @@
         <v>4</v>
       </c>
       <c r="M116" t="s">
-        <v>359</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -11810,7 +13017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780EB405-1306-498B-8ECF-F0CAF0815027}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F22A19-03EC-4BDD-8968-958D5F61A057}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11845,10 +13052,10 @@
         <v>170</v>
       </c>
       <c r="K3" t="s">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="L3" t="s">
-        <v>394</v>
+        <v>451</v>
       </c>
       <c r="M3" t="s">
         <v>173</v>
@@ -11856,10 +13063,10 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="C4" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="D4" t="s">
         <v>320</v>
@@ -11871,10 +13078,10 @@
         <v>228</v>
       </c>
       <c r="I4" t="s">
-        <v>386</v>
+        <v>443</v>
       </c>
       <c r="J4" t="s">
-        <v>395</v>
+        <v>452</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -11888,13 +13095,13 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="C5" t="s">
         <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>444</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -11903,10 +13110,10 @@
         <v>228</v>
       </c>
       <c r="I5" t="s">
-        <v>388</v>
+        <v>445</v>
       </c>
       <c r="J5" t="s">
-        <v>396</v>
+        <v>453</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
@@ -11920,13 +13127,13 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="C6" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="D6" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11935,10 +13142,10 @@
         <v>228</v>
       </c>
       <c r="I6" t="s">
-        <v>389</v>
+        <v>446</v>
       </c>
       <c r="J6" t="s">
-        <v>397</v>
+        <v>454</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
@@ -11952,13 +13159,13 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>448</v>
       </c>
       <c r="D7" t="s">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -11967,10 +13174,10 @@
         <v>228</v>
       </c>
       <c r="I7" t="s">
-        <v>392</v>
+        <v>449</v>
       </c>
       <c r="J7" t="s">
-        <v>398</v>
+        <v>455</v>
       </c>
       <c r="K7" t="s">
         <v>21</v>
@@ -11980,6 +13187,847 @@
       </c>
       <c r="M7" t="s">
         <v>232</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7047D8B0-2114-435A-AD31-E1DD530E6492}">
+  <dimension ref="B9:T29"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="9" spans="2:20">
+      <c r="B9" t="s">
+        <v>167</v>
+      </c>
+      <c r="K9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20">
+      <c r="B10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" t="s">
+        <v>457</v>
+      </c>
+      <c r="E10" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" t="s">
+        <v>171</v>
+      </c>
+      <c r="G10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I10" t="s">
+        <v>174</v>
+      </c>
+      <c r="K10" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" t="s">
+        <v>457</v>
+      </c>
+      <c r="M10" t="s">
+        <v>209</v>
+      </c>
+      <c r="N10" t="s">
+        <v>498</v>
+      </c>
+      <c r="O10" t="s">
+        <v>58</v>
+      </c>
+      <c r="P10" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>500</v>
+      </c>
+      <c r="R10" t="s">
+        <v>414</v>
+      </c>
+      <c r="S10" t="s">
+        <v>261</v>
+      </c>
+      <c r="T10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20">
+      <c r="B11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D11" t="s">
+        <v>459</v>
+      </c>
+      <c r="E11" t="s">
+        <v>460</v>
+      </c>
+      <c r="F11" t="s">
+        <v>461</v>
+      </c>
+      <c r="G11" t="s">
+        <v>461</v>
+      </c>
+      <c r="H11" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" t="s">
+        <v>179</v>
+      </c>
+      <c r="K11" t="s">
+        <v>458</v>
+      </c>
+      <c r="L11" t="s">
+        <v>459</v>
+      </c>
+      <c r="M11" t="s">
+        <v>502</v>
+      </c>
+      <c r="N11">
+        <v>595</v>
+      </c>
+      <c r="O11">
+        <v>50</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0.08</v>
+      </c>
+      <c r="T11" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20">
+      <c r="B12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" t="s">
+        <v>462</v>
+      </c>
+      <c r="D12" t="s">
+        <v>459</v>
+      </c>
+      <c r="E12" t="s">
+        <v>463</v>
+      </c>
+      <c r="F12" t="s">
+        <v>461</v>
+      </c>
+      <c r="G12" t="s">
+        <v>461</v>
+      </c>
+      <c r="H12" t="s">
+        <v>178</v>
+      </c>
+      <c r="I12" t="s">
+        <v>179</v>
+      </c>
+      <c r="K12" t="s">
+        <v>462</v>
+      </c>
+      <c r="L12" t="s">
+        <v>459</v>
+      </c>
+      <c r="M12" t="s">
+        <v>504</v>
+      </c>
+      <c r="N12">
+        <v>1427.1999999999998</v>
+      </c>
+      <c r="O12">
+        <v>50</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>0.08</v>
+      </c>
+      <c r="T12" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20">
+      <c r="B13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C13" t="s">
+        <v>464</v>
+      </c>
+      <c r="D13" t="s">
+        <v>459</v>
+      </c>
+      <c r="E13" t="s">
+        <v>465</v>
+      </c>
+      <c r="F13" t="s">
+        <v>461</v>
+      </c>
+      <c r="G13" t="s">
+        <v>461</v>
+      </c>
+      <c r="H13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" t="s">
+        <v>464</v>
+      </c>
+      <c r="L13" t="s">
+        <v>459</v>
+      </c>
+      <c r="M13" t="s">
+        <v>505</v>
+      </c>
+      <c r="N13">
+        <v>65.449999999999989</v>
+      </c>
+      <c r="O13">
+        <v>50</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0.08</v>
+      </c>
+      <c r="T13" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20">
+      <c r="B14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" t="s">
+        <v>466</v>
+      </c>
+      <c r="D14" t="s">
+        <v>459</v>
+      </c>
+      <c r="E14" t="s">
+        <v>467</v>
+      </c>
+      <c r="F14" t="s">
+        <v>461</v>
+      </c>
+      <c r="G14" t="s">
+        <v>461</v>
+      </c>
+      <c r="H14" t="s">
+        <v>178</v>
+      </c>
+      <c r="I14" t="s">
+        <v>179</v>
+      </c>
+      <c r="K14" t="s">
+        <v>466</v>
+      </c>
+      <c r="L14" t="s">
+        <v>459</v>
+      </c>
+      <c r="R14">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S14" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20">
+      <c r="B15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D15" t="s">
+        <v>459</v>
+      </c>
+      <c r="E15" t="s">
+        <v>469</v>
+      </c>
+      <c r="F15" t="s">
+        <v>461</v>
+      </c>
+      <c r="G15" t="s">
+        <v>461</v>
+      </c>
+      <c r="H15" t="s">
+        <v>178</v>
+      </c>
+      <c r="I15" t="s">
+        <v>179</v>
+      </c>
+      <c r="K15" t="s">
+        <v>468</v>
+      </c>
+      <c r="L15" t="s">
+        <v>459</v>
+      </c>
+      <c r="R15">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S15" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20">
+      <c r="B16" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" t="s">
+        <v>470</v>
+      </c>
+      <c r="D16" t="s">
+        <v>459</v>
+      </c>
+      <c r="E16" t="s">
+        <v>471</v>
+      </c>
+      <c r="F16" t="s">
+        <v>461</v>
+      </c>
+      <c r="G16" t="s">
+        <v>461</v>
+      </c>
+      <c r="H16" t="s">
+        <v>178</v>
+      </c>
+      <c r="I16" t="s">
+        <v>179</v>
+      </c>
+      <c r="K16" t="s">
+        <v>470</v>
+      </c>
+      <c r="L16" t="s">
+        <v>459</v>
+      </c>
+      <c r="R16">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S16" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19">
+      <c r="B17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" t="s">
+        <v>472</v>
+      </c>
+      <c r="D17" t="s">
+        <v>459</v>
+      </c>
+      <c r="E17" t="s">
+        <v>473</v>
+      </c>
+      <c r="F17" t="s">
+        <v>461</v>
+      </c>
+      <c r="G17" t="s">
+        <v>461</v>
+      </c>
+      <c r="H17" t="s">
+        <v>178</v>
+      </c>
+      <c r="I17" t="s">
+        <v>179</v>
+      </c>
+      <c r="K17" t="s">
+        <v>472</v>
+      </c>
+      <c r="L17" t="s">
+        <v>459</v>
+      </c>
+      <c r="R17">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S17" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D18" t="s">
+        <v>459</v>
+      </c>
+      <c r="E18" t="s">
+        <v>475</v>
+      </c>
+      <c r="F18" t="s">
+        <v>461</v>
+      </c>
+      <c r="G18" t="s">
+        <v>461</v>
+      </c>
+      <c r="H18" t="s">
+        <v>178</v>
+      </c>
+      <c r="I18" t="s">
+        <v>179</v>
+      </c>
+      <c r="K18" t="s">
+        <v>474</v>
+      </c>
+      <c r="L18" t="s">
+        <v>459</v>
+      </c>
+      <c r="R18">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S18" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="B19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" t="s">
+        <v>476</v>
+      </c>
+      <c r="D19" t="s">
+        <v>459</v>
+      </c>
+      <c r="E19" t="s">
+        <v>477</v>
+      </c>
+      <c r="F19" t="s">
+        <v>461</v>
+      </c>
+      <c r="G19" t="s">
+        <v>461</v>
+      </c>
+      <c r="H19" t="s">
+        <v>178</v>
+      </c>
+      <c r="I19" t="s">
+        <v>179</v>
+      </c>
+      <c r="K19" t="s">
+        <v>476</v>
+      </c>
+      <c r="L19" t="s">
+        <v>459</v>
+      </c>
+      <c r="R19">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S19" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C20" t="s">
+        <v>478</v>
+      </c>
+      <c r="D20" t="s">
+        <v>459</v>
+      </c>
+      <c r="E20" t="s">
+        <v>479</v>
+      </c>
+      <c r="F20" t="s">
+        <v>461</v>
+      </c>
+      <c r="G20" t="s">
+        <v>461</v>
+      </c>
+      <c r="H20" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20" t="s">
+        <v>179</v>
+      </c>
+      <c r="K20" t="s">
+        <v>478</v>
+      </c>
+      <c r="L20" t="s">
+        <v>459</v>
+      </c>
+      <c r="R20">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S20" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="B21" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" t="s">
+        <v>480</v>
+      </c>
+      <c r="D21" t="s">
+        <v>459</v>
+      </c>
+      <c r="E21" t="s">
+        <v>481</v>
+      </c>
+      <c r="F21" t="s">
+        <v>461</v>
+      </c>
+      <c r="G21" t="s">
+        <v>461</v>
+      </c>
+      <c r="H21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" t="s">
+        <v>179</v>
+      </c>
+      <c r="K21" t="s">
+        <v>480</v>
+      </c>
+      <c r="L21" t="s">
+        <v>459</v>
+      </c>
+      <c r="R21">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S21" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="B22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" t="s">
+        <v>482</v>
+      </c>
+      <c r="D22" t="s">
+        <v>459</v>
+      </c>
+      <c r="E22" t="s">
+        <v>483</v>
+      </c>
+      <c r="F22" t="s">
+        <v>461</v>
+      </c>
+      <c r="G22" t="s">
+        <v>461</v>
+      </c>
+      <c r="H22" t="s">
+        <v>178</v>
+      </c>
+      <c r="I22" t="s">
+        <v>179</v>
+      </c>
+      <c r="K22" t="s">
+        <v>482</v>
+      </c>
+      <c r="L22" t="s">
+        <v>459</v>
+      </c>
+      <c r="R22">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S22" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C23" t="s">
+        <v>484</v>
+      </c>
+      <c r="D23" t="s">
+        <v>459</v>
+      </c>
+      <c r="E23" t="s">
+        <v>485</v>
+      </c>
+      <c r="F23" t="s">
+        <v>461</v>
+      </c>
+      <c r="G23" t="s">
+        <v>461</v>
+      </c>
+      <c r="H23" t="s">
+        <v>178</v>
+      </c>
+      <c r="I23" t="s">
+        <v>179</v>
+      </c>
+      <c r="K23" t="s">
+        <v>484</v>
+      </c>
+      <c r="L23" t="s">
+        <v>459</v>
+      </c>
+      <c r="R23">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S23" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C24" t="s">
+        <v>486</v>
+      </c>
+      <c r="D24" t="s">
+        <v>459</v>
+      </c>
+      <c r="E24" t="s">
+        <v>487</v>
+      </c>
+      <c r="F24" t="s">
+        <v>461</v>
+      </c>
+      <c r="G24" t="s">
+        <v>461</v>
+      </c>
+      <c r="H24" t="s">
+        <v>178</v>
+      </c>
+      <c r="I24" t="s">
+        <v>179</v>
+      </c>
+      <c r="K24" t="s">
+        <v>486</v>
+      </c>
+      <c r="L24" t="s">
+        <v>459</v>
+      </c>
+      <c r="R24">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S24" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
+      <c r="B25" t="s">
+        <v>228</v>
+      </c>
+      <c r="C25" t="s">
+        <v>488</v>
+      </c>
+      <c r="D25" t="s">
+        <v>459</v>
+      </c>
+      <c r="E25" t="s">
+        <v>489</v>
+      </c>
+      <c r="F25" t="s">
+        <v>461</v>
+      </c>
+      <c r="G25" t="s">
+        <v>461</v>
+      </c>
+      <c r="H25" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" t="s">
+        <v>179</v>
+      </c>
+      <c r="K25" t="s">
+        <v>488</v>
+      </c>
+      <c r="L25" t="s">
+        <v>459</v>
+      </c>
+      <c r="R25">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S25" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C26" t="s">
+        <v>490</v>
+      </c>
+      <c r="D26" t="s">
+        <v>459</v>
+      </c>
+      <c r="E26" t="s">
+        <v>491</v>
+      </c>
+      <c r="F26" t="s">
+        <v>461</v>
+      </c>
+      <c r="G26" t="s">
+        <v>461</v>
+      </c>
+      <c r="H26" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" t="s">
+        <v>179</v>
+      </c>
+      <c r="K26" t="s">
+        <v>490</v>
+      </c>
+      <c r="L26" t="s">
+        <v>459</v>
+      </c>
+      <c r="R26">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S26" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" t="s">
+        <v>492</v>
+      </c>
+      <c r="D27" t="s">
+        <v>459</v>
+      </c>
+      <c r="E27" t="s">
+        <v>493</v>
+      </c>
+      <c r="F27" t="s">
+        <v>461</v>
+      </c>
+      <c r="G27" t="s">
+        <v>461</v>
+      </c>
+      <c r="H27" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" t="s">
+        <v>179</v>
+      </c>
+      <c r="K27" t="s">
+        <v>492</v>
+      </c>
+      <c r="L27" t="s">
+        <v>459</v>
+      </c>
+      <c r="R27">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S27" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" t="s">
+        <v>494</v>
+      </c>
+      <c r="D28" t="s">
+        <v>459</v>
+      </c>
+      <c r="E28" t="s">
+        <v>495</v>
+      </c>
+      <c r="F28" t="s">
+        <v>461</v>
+      </c>
+      <c r="G28" t="s">
+        <v>461</v>
+      </c>
+      <c r="H28" t="s">
+        <v>178</v>
+      </c>
+      <c r="I28" t="s">
+        <v>179</v>
+      </c>
+      <c r="K28" t="s">
+        <v>494</v>
+      </c>
+      <c r="L28" t="s">
+        <v>459</v>
+      </c>
+      <c r="R28">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S28" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="B29" t="s">
+        <v>228</v>
+      </c>
+      <c r="C29" t="s">
+        <v>496</v>
+      </c>
+      <c r="D29" t="s">
+        <v>459</v>
+      </c>
+      <c r="E29" t="s">
+        <v>497</v>
+      </c>
+      <c r="F29" t="s">
+        <v>461</v>
+      </c>
+      <c r="G29" t="s">
+        <v>461</v>
+      </c>
+      <c r="H29" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" t="s">
+        <v>179</v>
+      </c>
+      <c r="K29" t="s">
+        <v>496</v>
+      </c>
+      <c r="L29" t="s">
+        <v>459</v>
+      </c>
+      <c r="R29">
+        <v>7.7499999999999999E-3</v>
+      </c>
+      <c r="S29" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C86AF1F9-7875-471F-980E-22BF138F4F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{552E5C74-F895-4426-85D4-4D9C300B99EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -662,7 +662,7 @@
     <t>e_spv_HRV_001</t>
   </si>
   <si>
-    <t>solar resource in cluster 1</t>
+    <t>solar resource near Split (cluster 1)</t>
   </si>
   <si>
     <t>annual</t>
@@ -674,85 +674,85 @@
     <t>e_spv_HRV_002</t>
   </si>
   <si>
-    <t>solar resource in cluster 2</t>
+    <t>solar resource near Split (cluster 2)</t>
   </si>
   <si>
     <t>e_spv_HRV_003</t>
   </si>
   <si>
-    <t>solar resource in cluster 3</t>
+    <t>solar resource near Rijeka (cluster 3)</t>
   </si>
   <si>
     <t>e_spv_HRV_004</t>
   </si>
   <si>
-    <t>solar resource in cluster 4</t>
+    <t>solar resource near Rijeka (cluster 4)</t>
   </si>
   <si>
     <t>e_spv_HRV_005</t>
   </si>
   <si>
-    <t>solar resource in cluster 5</t>
+    <t>solar resource near Rijeka (cluster 5)</t>
   </si>
   <si>
     <t>e_spv_HRV_006</t>
   </si>
   <si>
-    <t>solar resource in cluster 6</t>
+    <t>solar resource near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>e_spv_HRV_007</t>
   </si>
   <si>
-    <t>solar resource in cluster 7</t>
+    <t>solar resource near Zadar (cluster 7)</t>
   </si>
   <si>
     <t>e_spv_HRV_008</t>
   </si>
   <si>
-    <t>solar resource in cluster 8</t>
+    <t>solar resource near Zagreb (cluster 8)</t>
   </si>
   <si>
     <t>e_spv_HRV_009</t>
   </si>
   <si>
-    <t>solar resource in cluster 9</t>
+    <t>solar resource near Varazdin (cluster 9)</t>
   </si>
   <si>
     <t>e_spv_HRV_010</t>
   </si>
   <si>
-    <t>solar resource in cluster 10</t>
+    <t>solar resource near Zagreb (cluster 10)</t>
   </si>
   <si>
     <t>e_spv_HRV_011</t>
   </si>
   <si>
-    <t>solar resource in cluster 11</t>
+    <t>solar resource near Osijek (cluster 11)</t>
   </si>
   <si>
     <t>e_spv_HRV_012</t>
   </si>
   <si>
-    <t>solar resource in cluster 12</t>
+    <t>solar resource near Osijek (cluster 12)</t>
   </si>
   <si>
     <t>e_spv_HRV_013</t>
   </si>
   <si>
-    <t>solar resource in cluster 13</t>
+    <t>solar resource near Osijek (cluster 13)</t>
   </si>
   <si>
     <t>e_spv_HRV_014</t>
   </si>
   <si>
-    <t>solar resource in cluster 14</t>
+    <t>solar resource near Zagreb (cluster 14)</t>
   </si>
   <si>
     <t>e_spv_HRV_015</t>
   </si>
   <si>
-    <t>solar resource in cluster 15</t>
+    <t>solar resource near Zagreb (cluster 15)</t>
   </si>
   <si>
     <t>~fi_t</t>
@@ -818,30 +818,84 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_HRV_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_003</t>
   </si>
   <si>
@@ -854,115 +908,91 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_HRV_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
+  </si>
+  <si>
     <t>e_Osijek_HRV</t>
   </si>
   <si>
-    <t>e_Ogulin_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Kutina_HRV</t>
-  </si>
-  <si>
     <t>e_Pula_HRV</t>
   </si>
   <si>
     <t>e_Kutina_HRV,e_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>e_Sibenik_HRV,e_Split_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Sibenik_HRV,e_KastelStari_HRV,e_Split_HRV</t>
-  </si>
-  <si>
     <t>e_Ogulin_HRV,e_Knin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>e_Sisak_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>e_Knin_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sisak_HRV,e_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>e_Vinkovci_HRV,e_Osijek_HRV</t>
+    <t>distr_wonelc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wonelc_won_HRV_005</t>
@@ -971,6 +1001,24 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wonelc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_HRV_007</t>
   </si>
   <si>
@@ -983,54 +1031,6 @@
     <t>connecting wind onshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wonelc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_HRV_003</t>
   </si>
   <si>
@@ -1043,12 +1043,51 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>elc_won_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_011</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_012</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_006</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_001</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
     <t>elc_won_HRV_005</t>
   </si>
   <si>
     <t>e_Knin_HRV,e_Sibenik_HRV</t>
   </si>
   <si>
+    <t>elc_won_HRV_004</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_won_HRV_013</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
+  </si>
+  <si>
     <t>elc_won_HRV_007</t>
   </si>
   <si>
@@ -1061,45 +1100,6 @@
     <t>e_Osijek_HRV,e_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>elc_won_HRV_002</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_010</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_013</t>
-  </si>
-  <si>
-    <t>e_Zagreb_HRV,e_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_011</t>
-  </si>
-  <si>
-    <t>e_VelikaGorica_HRV,e_Sesvete_HRV,e_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_012</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_006</t>
-  </si>
-  <si>
-    <t>e_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_001</t>
-  </si>
-  <si>
-    <t>e_Split_HRV</t>
-  </si>
-  <si>
-    <t>elc_won_HRV_004</t>
-  </si>
-  <si>
-    <t>e_Pula_HRV,e_Viskovo_HRV,e_Rijeka_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
     <t>elc_won_HRV_003</t>
   </si>
   <si>
@@ -1112,12 +1112,24 @@
     <t>e_Vinkovci_HRV</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_HRV_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_HRV_007</t>
   </si>
   <si>
@@ -1142,12 +1154,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_HRV_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_HRV_002</t>
   </si>
   <si>
@@ -1172,10 +1178,7 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_HRV_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>elc_wof_HRV_009</t>
   </si>
   <si>
     <t>elc_wof_HRV_010</t>
@@ -1184,6 +1187,12 @@
     <t>e_Sibenik_HRV</t>
   </si>
   <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>e_Sibenik_HRV,e_Knin_HRV,e_Ogulin_HRV</t>
+  </si>
+  <si>
     <t>elc_wof_HRV_007</t>
   </si>
   <si>
@@ -1196,12 +1205,6 @@
     <t>elc_wof_HRV_003</t>
   </si>
   <si>
-    <t>elc_wof_HRV_005</t>
-  </si>
-  <si>
-    <t>e_Sibenik_HRV,e_Knin_HRV,e_Ogulin_HRV</t>
-  </si>
-  <si>
     <t>elc_wof_HRV_002</t>
   </si>
   <si>
@@ -1214,151 +1217,148 @@
     <t>elc_wof_HRV_008</t>
   </si>
   <si>
-    <t>elc_wof_HRV_009</t>
-  </si>
-  <si>
     <t>e_won_HRV_001</t>
   </si>
   <si>
-    <t>wind resource in cluster 1</t>
+    <t>wind onshore resource near Split (cluster 1)</t>
   </si>
   <si>
     <t>e_won_HRV_002</t>
   </si>
   <si>
-    <t>wind resource in cluster 2</t>
+    <t>wind onshore resource near Split (cluster 2)</t>
   </si>
   <si>
     <t>e_won_HRV_003</t>
   </si>
   <si>
-    <t>wind resource in cluster 3</t>
+    <t>wind onshore resource near Rijeka (cluster 3)</t>
   </si>
   <si>
     <t>e_won_HRV_004</t>
   </si>
   <si>
-    <t>wind resource in cluster 4</t>
+    <t>wind onshore resource near Rijeka (cluster 4)</t>
   </si>
   <si>
     <t>e_won_HRV_005</t>
   </si>
   <si>
-    <t>wind resource in cluster 5</t>
+    <t>wind onshore resource near Split (cluster 5)</t>
   </si>
   <si>
     <t>e_won_HRV_006</t>
   </si>
   <si>
-    <t>wind resource in cluster 6</t>
+    <t>wind onshore resource near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>e_won_HRV_007</t>
   </si>
   <si>
-    <t>wind resource in cluster 7</t>
+    <t>wind onshore resource near Zadar (cluster 7)</t>
   </si>
   <si>
     <t>e_won_HRV_008</t>
   </si>
   <si>
-    <t>wind resource in cluster 8</t>
+    <t>wind onshore resource near Osijek (cluster 8)</t>
   </si>
   <si>
     <t>e_won_HRV_009</t>
   </si>
   <si>
-    <t>wind resource in cluster 9</t>
+    <t>wind onshore resource near Osijek (cluster 9)</t>
   </si>
   <si>
     <t>e_won_HRV_010</t>
   </si>
   <si>
-    <t>wind resource in cluster 10</t>
+    <t>wind onshore resource near Zagreb (cluster 10)</t>
   </si>
   <si>
     <t>e_won_HRV_011</t>
   </si>
   <si>
-    <t>wind resource in cluster 11</t>
+    <t>wind onshore resource near Zagreb (cluster 11)</t>
   </si>
   <si>
     <t>e_won_HRV_012</t>
   </si>
   <si>
-    <t>wind resource in cluster 12</t>
+    <t>wind onshore resource near Varazdin (cluster 12)</t>
   </si>
   <si>
     <t>e_won_HRV_013</t>
   </si>
   <si>
-    <t>wind resource in cluster 13</t>
+    <t>wind onshore resource near Zagreb (cluster 13)</t>
   </si>
   <si>
     <t>e_wof_HRV_001</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 1</t>
+    <t>wind offshore resource near Pula (cluster 1)</t>
   </si>
   <si>
     <t>e_wof_HRV_002</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 2</t>
+    <t>wind offshore resource near Split (cluster 2)</t>
   </si>
   <si>
     <t>e_wof_HRV_003</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 3</t>
+    <t>wind offshore resource near Split (cluster 3)</t>
   </si>
   <si>
     <t>e_wof_HRV_004</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 4</t>
+    <t>wind offshore resource near Split (cluster 4)</t>
   </si>
   <si>
     <t>e_wof_HRV_005</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 5</t>
+    <t>wind offshore resource near Zadar (cluster 5)</t>
   </si>
   <si>
     <t>e_wof_HRV_006</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 6</t>
+    <t>wind offshore resource near Zadar (cluster 6)</t>
   </si>
   <si>
     <t>e_wof_HRV_007</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 7</t>
+    <t>wind offshore resource near Split (cluster 7)</t>
   </si>
   <si>
     <t>e_wof_HRV_008</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 8</t>
+    <t>wind offshore resource near Split (cluster 8)</t>
   </si>
   <si>
     <t>e_wof_HRV_009</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 9</t>
+    <t>wind offshore resource near Split (cluster 9)</t>
   </si>
   <si>
     <t>e_wof_HRV_010</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 10</t>
+    <t>wind offshore resource near Split (cluster 10)</t>
   </si>
   <si>
     <t>e_wof_HRV_011</t>
   </si>
   <si>
-    <t>wind offshore resource in cluster 11</t>
+    <t>wind offshore resource near Split (cluster 11)</t>
   </si>
   <si>
     <t>~fi_t: UP</t>
@@ -6467,7 +6467,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C50DD9-4E38-4635-90D0-ABBAFAF9AFF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{500D8E34-39FC-4775-8904-19699AA2F953}">
   <dimension ref="B9:BD25"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6705,16 +6705,16 @@
         <v>229</v>
       </c>
       <c r="Y11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="Z11" t="s">
         <v>263</v>
       </c>
       <c r="AA11">
-        <v>0.99833598914935617</v>
+        <v>0.99867337680137247</v>
       </c>
       <c r="AB11">
-        <v>30.506865595137178</v>
+        <v>24.321425308170515</v>
       </c>
       <c r="AD11" t="s">
         <v>228</v>
@@ -6744,13 +6744,13 @@
         <v>304</v>
       </c>
       <c r="AN11" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="AO11">
-        <v>0.99864406184009369</v>
+        <v>0.99916796132064933</v>
       </c>
       <c r="AP11">
-        <v>24.858866264948823</v>
+        <v>15.254042454762756</v>
       </c>
       <c r="AR11" t="s">
         <v>228</v>
@@ -6780,13 +6780,13 @@
         <v>349</v>
       </c>
       <c r="BB11" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="BC11">
-        <v>0.99349673079251344</v>
+        <v>0.99654308092357613</v>
       </c>
       <c r="BD11">
-        <v>119.22660213725317</v>
+        <v>556.11662437297844</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6851,16 +6851,16 @@
         <v>233</v>
       </c>
       <c r="Y12" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="Z12" t="s">
         <v>264</v>
       </c>
       <c r="AA12">
-        <v>0.99841413454839123</v>
+        <v>0.99878927154998876</v>
       </c>
       <c r="AB12">
-        <v>29.074199946161183</v>
+        <v>22.196688250206851</v>
       </c>
       <c r="AD12" t="s">
         <v>228</v>
@@ -6887,16 +6887,16 @@
         <v>280</v>
       </c>
       <c r="AM12" t="s">
+        <v>305</v>
+      </c>
+      <c r="AN12" t="s">
         <v>306</v>
       </c>
-      <c r="AN12" t="s">
-        <v>307</v>
-      </c>
       <c r="AO12">
-        <v>0.99831383758599213</v>
+        <v>0.99868561654722476</v>
       </c>
       <c r="AP12">
-        <v>30.912977590144003</v>
+        <v>24.097029967546128</v>
       </c>
       <c r="AR12" t="s">
         <v>228</v>
@@ -6923,16 +6923,16 @@
         <v>329</v>
       </c>
       <c r="BA12" t="s">
+        <v>350</v>
+      </c>
+      <c r="BB12" t="s">
         <v>351</v>
       </c>
-      <c r="BB12" t="s">
-        <v>268</v>
-      </c>
       <c r="BC12">
-        <v>0.99748881051271865</v>
+        <v>0.99349673079251344</v>
       </c>
       <c r="BD12">
-        <v>46.038473933492185</v>
+        <v>783.57743415899472</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6997,16 +6997,16 @@
         <v>235</v>
       </c>
       <c r="Y13" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="Z13" t="s">
         <v>265</v>
       </c>
       <c r="AA13">
-        <v>0.99606139674621874</v>
+        <v>0.99841413454839123</v>
       </c>
       <c r="AB13">
-        <v>72.207726319322958</v>
+        <v>29.074199946161183</v>
       </c>
       <c r="AD13" t="s">
         <v>228</v>
@@ -7033,16 +7033,16 @@
         <v>282</v>
       </c>
       <c r="AM13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AN13" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="AO13">
-        <v>0.99806647110300117</v>
+        <v>0.99599733612049879</v>
       </c>
       <c r="AP13">
-        <v>35.448029778312126</v>
+        <v>73.382171124189711</v>
       </c>
       <c r="AR13" t="s">
         <v>228</v>
@@ -7072,13 +7072,13 @@
         <v>352</v>
       </c>
       <c r="BB13" t="s">
-        <v>268</v>
+        <v>353</v>
       </c>
       <c r="BC13">
-        <v>0.99261900653330459</v>
+        <v>0.99274877595658639</v>
       </c>
       <c r="BD13">
-        <v>135.31821355608193</v>
+        <v>839.4247285748836</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7143,16 +7143,16 @@
         <v>237</v>
       </c>
       <c r="Y14" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="Z14" t="s">
         <v>266</v>
       </c>
       <c r="AA14">
-        <v>0.99752410262804614</v>
+        <v>0.99606139674621874</v>
       </c>
       <c r="AB14">
-        <v>45.391451819153936</v>
+        <v>72.207726319322958</v>
       </c>
       <c r="AD14" t="s">
         <v>228</v>
@@ -7179,16 +7179,16 @@
         <v>284</v>
       </c>
       <c r="AM14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AN14" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="AO14">
-        <v>0.99916796132064933</v>
+        <v>0.99696949512524791</v>
       </c>
       <c r="AP14">
-        <v>15.254042454762756</v>
+        <v>55.559256037121919</v>
       </c>
       <c r="AR14" t="s">
         <v>228</v>
@@ -7215,16 +7215,16 @@
         <v>333</v>
       </c>
       <c r="BA14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="BB14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="BC14">
-        <v>0.99471849364594245</v>
+        <v>0.99748881051271865</v>
       </c>
       <c r="BD14">
-        <v>96.827616491055764</v>
+        <v>485.50214838367731</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7289,16 +7289,16 @@
         <v>239</v>
       </c>
       <c r="Y15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z15" t="s">
         <v>267</v>
       </c>
       <c r="AA15">
-        <v>0.99663785488220757</v>
+        <v>0.99790259024057815</v>
       </c>
       <c r="AB15">
-        <v>61.639327159526964</v>
+        <v>38.452512256066314</v>
       </c>
       <c r="AD15" t="s">
         <v>228</v>
@@ -7325,16 +7325,16 @@
         <v>286</v>
       </c>
       <c r="AM15" t="s">
+        <v>310</v>
+      </c>
+      <c r="AN15" t="s">
         <v>311</v>
       </c>
-      <c r="AN15" t="s">
-        <v>273</v>
-      </c>
       <c r="AO15">
-        <v>0.99855068763113897</v>
+        <v>0.99309131353273861</v>
       </c>
       <c r="AP15">
-        <v>26.570726762452622</v>
+        <v>126.6592518997923</v>
       </c>
       <c r="AR15" t="s">
         <v>228</v>
@@ -7361,16 +7361,16 @@
         <v>335</v>
       </c>
       <c r="BA15" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="BB15" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="BC15">
-        <v>0.98623672902883308</v>
+        <v>0.99261900653330459</v>
       </c>
       <c r="BD15">
-        <v>252.32663447139444</v>
+        <v>849.11417884658817</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7435,16 +7435,16 @@
         <v>241</v>
       </c>
       <c r="Y16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Z16" t="s">
         <v>268</v>
       </c>
       <c r="AA16">
-        <v>0.99751404781443698</v>
+        <v>0.99744104449393167</v>
       </c>
       <c r="AB16">
-        <v>45.575790068655763</v>
+        <v>46.914184277920093</v>
       </c>
       <c r="AD16" t="s">
         <v>228</v>
@@ -7477,10 +7477,10 @@
         <v>313</v>
       </c>
       <c r="AO16">
-        <v>0.99661124612196206</v>
+        <v>0.99864406184009369</v>
       </c>
       <c r="AP16">
-        <v>62.127154430695668</v>
+        <v>24.858866264948823</v>
       </c>
       <c r="AR16" t="s">
         <v>228</v>
@@ -7507,16 +7507,16 @@
         <v>337</v>
       </c>
       <c r="BA16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="BB16" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="BC16">
-        <v>0.99274877595658639</v>
+        <v>0.99471849364594245</v>
       </c>
       <c r="BD16">
-        <v>132.93910746258302</v>
+        <v>692.35247443629987</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7581,16 +7581,16 @@
         <v>243</v>
       </c>
       <c r="Y17" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Z17" t="s">
         <v>269</v>
       </c>
       <c r="AA17">
-        <v>0.99862410236781662</v>
+        <v>0.99817092025513499</v>
       </c>
       <c r="AB17">
-        <v>25.224789923361115</v>
+        <v>33.533128655859528</v>
       </c>
       <c r="AD17" t="s">
         <v>228</v>
@@ -7623,10 +7623,10 @@
         <v>315</v>
       </c>
       <c r="AO17">
-        <v>0.99868561654722476</v>
+        <v>0.99842569630166256</v>
       </c>
       <c r="AP17">
-        <v>24.097029967546128</v>
+        <v>28.86223446951988</v>
       </c>
       <c r="AR17" t="s">
         <v>228</v>
@@ -7656,13 +7656,13 @@
         <v>357</v>
       </c>
       <c r="BB17" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="BC17">
-        <v>0.99303722633601399</v>
+        <v>0.98623672902883308</v>
       </c>
       <c r="BD17">
-        <v>127.65085050641102</v>
+        <v>1073.2735505867265</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7727,16 +7727,16 @@
         <v>245</v>
       </c>
       <c r="Y18" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z18" t="s">
         <v>270</v>
       </c>
       <c r="AA18">
-        <v>0.99746297747029244</v>
+        <v>0.99608191256693812</v>
       </c>
       <c r="AB18">
-        <v>46.512079711305255</v>
+        <v>71.831602939467288</v>
       </c>
       <c r="AD18" t="s">
         <v>228</v>
@@ -7766,13 +7766,13 @@
         <v>316</v>
       </c>
       <c r="AN18" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="AO18">
-        <v>0.99599733612049879</v>
+        <v>0.99855068763113897</v>
       </c>
       <c r="AP18">
-        <v>73.382171124189711</v>
+        <v>26.570726762452622</v>
       </c>
       <c r="AR18" t="s">
         <v>228</v>
@@ -7802,13 +7802,13 @@
         <v>358</v>
       </c>
       <c r="BB18" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="BC18">
-        <v>0.99176701066797779</v>
+        <v>0.99303722633601399</v>
       </c>
       <c r="BD18">
-        <v>150.93813775374051</v>
+        <v>817.88710024429213</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7873,16 +7873,16 @@
         <v>247</v>
       </c>
       <c r="Y19" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z19" t="s">
         <v>271</v>
       </c>
       <c r="AA19">
-        <v>0.99790259024057815</v>
+        <v>0.99696148198205803</v>
       </c>
       <c r="AB19">
-        <v>38.452512256066314</v>
+        <v>55.706163662270022</v>
       </c>
       <c r="AD19" t="s">
         <v>228</v>
@@ -7915,10 +7915,10 @@
         <v>318</v>
       </c>
       <c r="AO19">
-        <v>0.99696949512524791</v>
+        <v>0.99661124612196206</v>
       </c>
       <c r="AP19">
-        <v>55.559256037121919</v>
+        <v>62.127154430695668</v>
       </c>
       <c r="AR19" t="s">
         <v>228</v>
@@ -7948,13 +7948,13 @@
         <v>359</v>
       </c>
       <c r="BB19" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="BC19">
-        <v>0.9956307614354567</v>
+        <v>0.99176701066797779</v>
       </c>
       <c r="BD19">
-        <v>80.102707016626312</v>
+        <v>912.72987012432498</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8019,16 +8019,16 @@
         <v>249</v>
       </c>
       <c r="Y20" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Z20" t="s">
         <v>272</v>
       </c>
       <c r="AA20">
-        <v>0.99867337680137247</v>
+        <v>0.99751404781443698</v>
       </c>
       <c r="AB20">
-        <v>24.321425308170515</v>
+        <v>45.575790068655763</v>
       </c>
       <c r="AD20" t="s">
         <v>228</v>
@@ -8061,10 +8061,10 @@
         <v>320</v>
       </c>
       <c r="AO20">
-        <v>0.99309131353273861</v>
+        <v>0.99831383758599213</v>
       </c>
       <c r="AP20">
-        <v>126.6592518997923</v>
+        <v>30.912977590144003</v>
       </c>
       <c r="AR20" t="s">
         <v>228</v>
@@ -8094,13 +8094,13 @@
         <v>360</v>
       </c>
       <c r="BB20" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="BC20">
-        <v>0.9950151616455658</v>
+        <v>0.9956307614354567</v>
       </c>
       <c r="BD20">
-        <v>91.388703164627643</v>
+        <v>624.23647948589633</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8165,16 +8165,16 @@
         <v>251</v>
       </c>
       <c r="Y21" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="Z21" t="s">
         <v>273</v>
       </c>
       <c r="AA21">
-        <v>0.99878927154998876</v>
+        <v>0.99862410236781662</v>
       </c>
       <c r="AB21">
-        <v>22.196688250206851</v>
+        <v>25.224789923361115</v>
       </c>
       <c r="AD21" t="s">
         <v>228</v>
@@ -8207,10 +8207,10 @@
         <v>322</v>
       </c>
       <c r="AO21">
-        <v>0.99842569630166256</v>
+        <v>0.99806647110300117</v>
       </c>
       <c r="AP21">
-        <v>28.86223446951988</v>
+        <v>35.448029778312126</v>
       </c>
       <c r="AR21" t="s">
         <v>228</v>
@@ -8240,13 +8240,13 @@
         <v>361</v>
       </c>
       <c r="BB21" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="BC21">
-        <v>0.99654308092357613</v>
+        <v>0.9950151616455658</v>
       </c>
       <c r="BD21">
-        <v>63.376849734436668</v>
+        <v>670.20126379775616</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8311,16 +8311,16 @@
         <v>253</v>
       </c>
       <c r="Y22" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Z22" t="s">
         <v>274</v>
       </c>
       <c r="AA22">
-        <v>0.99744104449393167</v>
+        <v>0.99833598914935617</v>
       </c>
       <c r="AB22">
-        <v>46.914184277920093</v>
+        <v>30.506865595137178</v>
       </c>
       <c r="AD22" t="s">
         <v>228</v>
@@ -8421,16 +8421,16 @@
         <v>255</v>
       </c>
       <c r="Y23" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="Z23" t="s">
         <v>275</v>
       </c>
       <c r="AA23">
-        <v>0.99817092025513499</v>
+        <v>0.99752410262804614</v>
       </c>
       <c r="AB23">
-        <v>33.533128655859528</v>
+        <v>45.391451819153936</v>
       </c>
       <c r="AD23" t="s">
         <v>228</v>
@@ -8531,16 +8531,16 @@
         <v>257</v>
       </c>
       <c r="Y24" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Z24" t="s">
         <v>276</v>
       </c>
       <c r="AA24">
-        <v>0.99608191256693812</v>
+        <v>0.99663785488220757</v>
       </c>
       <c r="AB24">
-        <v>71.831602939467288</v>
+        <v>61.639327159526964</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8605,16 +8605,16 @@
         <v>259</v>
       </c>
       <c r="Y25" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="Z25" t="s">
         <v>277</v>
       </c>
       <c r="AA25">
-        <v>0.99696148198205803</v>
+        <v>0.99746297747029244</v>
       </c>
       <c r="AB25">
-        <v>55.706163662270022</v>
+        <v>46.512079711305255</v>
       </c>
     </row>
   </sheetData>
@@ -8623,7 +8623,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB73AA55-1319-4E16-9823-8E5F3816DB39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D8ED9F-A4AE-4F72-B604-904A0496D155}">
   <dimension ref="B9:Z23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -8735,7 +8735,7 @@
         <v>362</v>
       </c>
       <c r="K11" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="L11">
         <v>9.2886312097189838E-2</v>
@@ -8768,7 +8768,7 @@
         <v>388</v>
       </c>
       <c r="X11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Y11">
         <v>4.1159999999999997</v>
@@ -8803,7 +8803,7 @@
         <v>364</v>
       </c>
       <c r="K12" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L12">
         <v>0.1738962180995865</v>
@@ -8836,7 +8836,7 @@
         <v>390</v>
       </c>
       <c r="X12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y12">
         <v>13.587</v>
@@ -8904,7 +8904,7 @@
         <v>392</v>
       </c>
       <c r="X13" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Y13">
         <v>2.415</v>
@@ -8939,7 +8939,7 @@
         <v>368</v>
       </c>
       <c r="K14" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L14">
         <v>5.1128062243546414E-2</v>
@@ -8972,7 +8972,7 @@
         <v>394</v>
       </c>
       <c r="X14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Y14">
         <v>6.5782499999999997</v>
@@ -9007,7 +9007,7 @@
         <v>370</v>
       </c>
       <c r="K15" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="L15">
         <v>1.073704635262974</v>
@@ -9040,7 +9040,7 @@
         <v>396</v>
       </c>
       <c r="X15" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Y15">
         <v>9.5145</v>
@@ -9075,7 +9075,7 @@
         <v>372</v>
       </c>
       <c r="K16" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="L16">
         <v>2.5331182456020541E-2</v>
@@ -9108,7 +9108,7 @@
         <v>398</v>
       </c>
       <c r="X16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y16">
         <v>13.50075</v>
@@ -9143,7 +9143,7 @@
         <v>374</v>
       </c>
       <c r="K17" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="L17">
         <v>0.40509336740495844</v>
@@ -9176,7 +9176,7 @@
         <v>400</v>
       </c>
       <c r="X17" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Y17">
         <v>5.1029999999999998</v>
@@ -9244,7 +9244,7 @@
         <v>402</v>
       </c>
       <c r="X18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Y18">
         <v>6.9870000000000001</v>
@@ -9279,7 +9279,7 @@
         <v>378</v>
       </c>
       <c r="K19" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="L19">
         <v>1.0612229212113009</v>
@@ -9312,7 +9312,7 @@
         <v>404</v>
       </c>
       <c r="X19" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="Y19">
         <v>5.6325000000000003</v>
@@ -9347,7 +9347,7 @@
         <v>380</v>
       </c>
       <c r="K20" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="L20">
         <v>0.26698243467862187</v>
@@ -9380,7 +9380,7 @@
         <v>406</v>
       </c>
       <c r="X20" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Y20">
         <v>9.4177499999999998</v>
@@ -9415,7 +9415,7 @@
         <v>382</v>
       </c>
       <c r="K21" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="L21">
         <v>9.4990726367794626E-2</v>
@@ -9448,7 +9448,7 @@
         <v>408</v>
       </c>
       <c r="X21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Y21">
         <v>7.4775</v>
@@ -9483,7 +9483,7 @@
         <v>384</v>
       </c>
       <c r="K22" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="L22">
         <v>0.67786060958439753</v>
@@ -9518,7 +9518,7 @@
         <v>386</v>
       </c>
       <c r="K23" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="L23">
         <v>1.1726864883934578</v>
@@ -9533,7 +9533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{711220C6-5BD3-4303-8CAE-DB174FB160E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{849FAE54-00B9-4E14-B988-02E42B88FADE}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13017,7 +13017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F22A19-03EC-4BDD-8968-958D5F61A057}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B173101-1785-41C1-BCA9-4A9B85C8CE1A}">
   <dimension ref="B2:M7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13069,7 +13069,7 @@
         <v>444</v>
       </c>
       <c r="D4" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -13098,7 +13098,7 @@
         <v>445</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="D5" t="s">
         <v>444</v>
@@ -13195,7 +13195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7047D8B0-2114-435A-AD31-E1DD530E6492}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F31E1511-1E41-4AFA-AD64-19C2C2424DE9}">
   <dimension ref="B9:T29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
